--- a/kinit-api/scripts/initialize/data/init.xlsx
+++ b/kinit-api/scripts/initialize/data/init.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24332"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\ktianc\programming\project\kinit-pro\kinit-api\scripts\initialize\data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35F03963-B92D-4400-A571-635978E5B7B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="887" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="27660" windowHeight="13660" tabRatio="887" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="vadmin_auth_menu" sheetId="1" r:id="rId1"/>
@@ -26,12 +20,25 @@
     <sheet name="vadmin_auth_dept" sheetId="12" r:id="rId11"/>
     <sheet name="vadmin_auth_user_depts" sheetId="13" r:id="rId12"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="350">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="497" uniqueCount="348">
   <si>
     <t>title</t>
   </si>
@@ -153,6 +160,9 @@
     <t>数据概览</t>
   </si>
   <si>
+    <t>views/Dashboard/Analysis/Analysis</t>
+  </si>
+  <si>
     <t>analysis</t>
   </si>
   <si>
@@ -168,45 +178,72 @@
     <t>菜单管理</t>
   </si>
   <si>
+    <t>views/Vadmin/Auth/Menu/Menu</t>
+  </si>
+  <si>
     <t>menu</t>
   </si>
   <si>
     <t>角色管理</t>
   </si>
   <si>
+    <t>views/Vadmin/Auth/Role/Role</t>
+  </si>
+  <si>
     <t>role</t>
   </si>
   <si>
     <t>用户管理</t>
   </si>
   <si>
+    <t>views/Vadmin/Auth/User/User</t>
+  </si>
+  <si>
     <t>user</t>
   </si>
   <si>
     <t>字典配置</t>
   </si>
   <si>
+    <t>views/Vadmin/System/Dict/Dict</t>
+  </si>
+  <si>
     <t>dict</t>
   </si>
   <si>
     <t>日志管理</t>
   </si>
   <si>
+    <t>tdesign:catalog</t>
+  </si>
+  <si>
+    <t>/record</t>
+  </si>
+  <si>
     <t>系统配置</t>
   </si>
   <si>
+    <t>views/Vadmin/System/Settings/Settings</t>
+  </si>
+  <si>
     <t>settings</t>
   </si>
   <si>
     <t>登录日志</t>
   </si>
   <si>
+    <t>views/Vadmin/System/Record/Login/Login</t>
+  </si>
+  <si>
     <t>login</t>
   </si>
   <si>
     <t>操作日志</t>
   </si>
   <si>
+    <t>views/Vadmin/System/Record/Operation/Operation</t>
+  </si>
+  <si>
     <t>operation</t>
   </si>
   <si>
@@ -297,18 +334,27 @@
     <t>常见问题类别</t>
   </si>
   <si>
+    <t>views/Vadmin/Help/IssueCategory/IssueCategory</t>
+  </si>
+  <si>
     <t>issue/category</t>
   </si>
   <si>
     <t>常见问题</t>
   </si>
   <si>
+    <t>views/Vadmin/Help/Issue/Issue</t>
+  </si>
+  <si>
     <t>issue</t>
   </si>
   <si>
     <t>常见问题表单</t>
   </si>
   <si>
+    <t>views/Vadmin/Help/Issue/components/Write</t>
+  </si>
+  <si>
     <t>issue/form</t>
   </si>
   <si>
@@ -327,18 +373,27 @@
     <t>空气质量</t>
   </si>
   <si>
+    <t>views/Vadmin/Screen/Air/Air</t>
+  </si>
+  <si>
     <t>air</t>
   </si>
   <si>
     <t>定时任务</t>
   </si>
   <si>
+    <t>views/Vadmin/System/Task/Task</t>
+  </si>
+  <si>
     <t>task</t>
   </si>
   <si>
     <t>调度日志</t>
   </si>
   <si>
+    <t>views/Vadmin/System/Record/Task/Task</t>
+  </si>
+  <si>
     <t>获取菜单列表</t>
   </si>
   <si>
@@ -369,9 +424,21 @@
     <t>图片资源</t>
   </si>
   <si>
+    <t>views/Vadmin/Resource/Image/Image</t>
+  </si>
+  <si>
     <t>images</t>
   </si>
   <si>
+    <t>部门管理</t>
+  </si>
+  <si>
+    <t>views/Vadmin/Auth/Dept/Dept</t>
+  </si>
+  <si>
+    <t>dept</t>
+  </si>
+  <si>
     <t>name</t>
   </si>
   <si>
@@ -384,24 +451,30 @@
     <t>is_admin</t>
   </si>
   <si>
+    <t>data_range</t>
+  </si>
+  <si>
     <t>管理员</t>
   </si>
   <si>
     <t>admin</t>
   </si>
   <si>
+    <t>avatar</t>
+  </si>
+  <si>
     <t>telephone</t>
   </si>
   <si>
+    <t>email</t>
+  </si>
+  <si>
     <t>nickname</t>
   </si>
   <si>
     <t>password</t>
   </si>
   <si>
-    <t>avatar</t>
-  </si>
-  <si>
     <t>gender</t>
   </si>
   <si>
@@ -420,7 +493,10 @@
     <t>is_staff</t>
   </si>
   <si>
-    <t>15020221010</t>
+    <t>wx_server_openid</t>
+  </si>
+  <si>
+    <t>is_wx_server_openid</t>
   </si>
   <si>
     <t>kinit</t>
@@ -436,7 +512,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>u</t>
     </r>
@@ -444,7 +520,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>ser_id</t>
     </r>
@@ -454,7 +530,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>r</t>
     </r>
@@ -462,7 +538,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>ole_id</t>
     </r>
@@ -510,18 +586,24 @@
     <t>与定时任务中有约定，请勿随意更改</t>
   </si>
   <si>
+    <t>数据权限范围</t>
+  </si>
+  <si>
+    <t>sys_vadmin_data_range</t>
+  </si>
+  <si>
+    <t>label</t>
+  </si>
+  <si>
+    <t>value</t>
+  </si>
+  <si>
     <t>is_default</t>
   </si>
   <si>
     <t>dict_type_id</t>
   </si>
   <si>
-    <t>label</t>
-  </si>
-  <si>
-    <t>value</t>
-  </si>
-  <si>
     <t>男</t>
   </si>
   <si>
@@ -568,6 +650,27 @@
   </si>
   <si>
     <t>date</t>
+  </si>
+  <si>
+    <t>仅本人数据权限</t>
+  </si>
+  <si>
+    <t>本部门数据权限</t>
+  </si>
+  <si>
+    <t>本部门及以下数据权限</t>
+  </si>
+  <si>
+    <t>自定义数据权限</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>全部数据权限</t>
+  </si>
+  <si>
+    <t>4</t>
   </si>
   <si>
     <t>tab_label</t>
@@ -991,51 +1094,6 @@
     <t>&lt;p&gt;请点击[我的] - [应用设置] - [修改密码]即可修改登录密码&lt;/p&gt;</t>
   </si>
   <si>
-    <t>views/Dashboard/Analysis/Analysis</t>
-  </si>
-  <si>
-    <t>views/Vadmin/Auth/Menu/Menu</t>
-  </si>
-  <si>
-    <t>views/Vadmin/Auth/Role/Role</t>
-  </si>
-  <si>
-    <t>views/Vadmin/Auth/User/User</t>
-  </si>
-  <si>
-    <t>views/Vadmin/System/Dict/Dict</t>
-  </si>
-  <si>
-    <t>views/Vadmin/System/Settings/Settings</t>
-  </si>
-  <si>
-    <t>views/Vadmin/System/Record/Login/Login</t>
-  </si>
-  <si>
-    <t>views/Vadmin/System/Record/Operation/Operation</t>
-  </si>
-  <si>
-    <t>views/Vadmin/Help/IssueCategory/IssueCategory</t>
-  </si>
-  <si>
-    <t>views/Vadmin/Help/Issue/Issue</t>
-  </si>
-  <si>
-    <t>views/Vadmin/Help/Issue/components/Write</t>
-  </si>
-  <si>
-    <t>views/Vadmin/Screen/Air/Air</t>
-  </si>
-  <si>
-    <t>views/Vadmin/System/Task/Task</t>
-  </si>
-  <si>
-    <t>views/Vadmin/System/Record/Task/Task</t>
-  </si>
-  <si>
-    <t>views/Vadmin/Resource/Image/Image</t>
-  </si>
-  <si>
     <t>dept_key</t>
   </si>
   <si>
@@ -1045,9 +1103,6 @@
     <t>phone</t>
   </si>
   <si>
-    <t>email</t>
-  </si>
-  <si>
     <t>kinit 开发团队</t>
   </si>
   <si>
@@ -1058,71 +1113,20 @@
   </si>
   <si>
     <t>dept_id</t>
-  </si>
-  <si>
-    <t>tdesign:catalog</t>
-  </si>
-  <si>
-    <t>/record</t>
-  </si>
-  <si>
-    <t>部门管理</t>
-  </si>
-  <si>
-    <t>views/Vadmin/Auth/Dept/Dept</t>
-  </si>
-  <si>
-    <t>dept</t>
-  </si>
-  <si>
-    <t>data_range</t>
-  </si>
-  <si>
-    <t>wx_server_openid</t>
-  </si>
-  <si>
-    <t>is_wx_server_openid</t>
-  </si>
-  <si>
-    <t>数据权限范围</t>
-  </si>
-  <si>
-    <t>sys_vadmin_data_range</t>
-  </si>
-  <si>
-    <t>仅本人数据权限</t>
-  </si>
-  <si>
-    <t>本部门数据权限</t>
-  </si>
-  <si>
-    <t>本部门及以下数据权限</t>
-  </si>
-  <si>
-    <t>自定义数据权限</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>全部数据权限</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>系统配置</t>
-    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="5">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="yyyy/m/d\ h:mm:ss"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -1143,30 +1147,353 @@
     </font>
     <font>
       <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -1174,34 +1501,316 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="超链接" xfId="1" builtinId="8"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1459,14 +2068,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:V41"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1" spans="1:22">
       <c r="A1" t="s">
@@ -1586,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="S2" s="1">
-        <v>44786.455925925926</v>
+        <v>44786.4559259259</v>
       </c>
       <c r="T2" s="1">
-        <v>45204.098263888889</v>
+        <v>45204.0982638889</v>
       </c>
       <c r="V2">
         <v>0</v>
@@ -1645,10 +2254,10 @@
         <v>2</v>
       </c>
       <c r="S3" s="1">
-        <v>44826.954074074078</v>
+        <v>44826.9540740741</v>
       </c>
       <c r="T3" s="1">
-        <v>45204.099050925928</v>
+        <v>45204.0990509259</v>
       </c>
       <c r="V3">
         <v>0</v>
@@ -1701,10 +2310,10 @@
         <v>3</v>
       </c>
       <c r="S4" s="1">
-        <v>44838.873819444445</v>
+        <v>44838.8738194444</v>
       </c>
       <c r="T4" s="1">
-        <v>44862.894594907404</v>
+        <v>44862.8945949074</v>
       </c>
       <c r="V4">
         <v>0</v>
@@ -1757,10 +2366,10 @@
         <v>4</v>
       </c>
       <c r="S5" s="1">
-        <v>44846.707951388889</v>
+        <v>44846.7079513889</v>
       </c>
       <c r="T5" s="1">
-        <v>44883.434432870366</v>
+        <v>44883.4344328704</v>
       </c>
       <c r="V5">
         <v>0</v>
@@ -1771,10 +2380,10 @@
         <v>39</v>
       </c>
       <c r="D6" t="s">
-        <v>309</v>
+        <v>40</v>
       </c>
       <c r="E6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -1813,10 +2422,10 @@
         <v>5</v>
       </c>
       <c r="S6" s="1">
-        <v>44870.538877314815</v>
+        <v>44870.5388773148</v>
       </c>
       <c r="T6" s="1">
-        <v>45183.673703703702</v>
+        <v>45183.6737037037</v>
       </c>
       <c r="V6">
         <v>0</v>
@@ -1824,13 +2433,13 @@
     </row>
     <row r="7" spans="1:22">
       <c r="A7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -1869,10 +2478,10 @@
         <v>6</v>
       </c>
       <c r="S7" s="1">
-        <v>44881.777280092596</v>
+        <v>44881.7772800926</v>
       </c>
       <c r="T7" s="1">
-        <v>44882.864988425928</v>
+        <v>44882.8649884259</v>
       </c>
       <c r="V7">
         <v>0</v>
@@ -1880,13 +2489,13 @@
     </row>
     <row r="8" spans="1:22">
       <c r="A8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D8" t="s">
-        <v>310</v>
+        <v>46</v>
       </c>
       <c r="E8" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -1925,10 +2534,10 @@
         <v>7</v>
       </c>
       <c r="S8" s="1">
-        <v>44826.723263888889</v>
+        <v>44826.7232638889</v>
       </c>
       <c r="T8" s="1">
-        <v>44883.435208333329</v>
+        <v>44883.4352083333</v>
       </c>
       <c r="V8">
         <v>0</v>
@@ -1936,13 +2545,13 @@
     </row>
     <row r="9" spans="1:22">
       <c r="A9" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D9" t="s">
-        <v>311</v>
+        <v>49</v>
       </c>
       <c r="E9" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -1981,10 +2590,10 @@
         <v>8</v>
       </c>
       <c r="S9" s="1">
-        <v>44826.723263888889</v>
+        <v>44826.7232638889</v>
       </c>
       <c r="T9" s="1">
-        <v>44883.435370370367</v>
+        <v>44883.4353703704</v>
       </c>
       <c r="V9">
         <v>0</v>
@@ -1992,13 +2601,13 @@
     </row>
     <row r="10" spans="1:22">
       <c r="A10" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D10" t="s">
-        <v>312</v>
+        <v>52</v>
       </c>
       <c r="E10" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -2037,10 +2646,10 @@
         <v>9</v>
       </c>
       <c r="S10" s="1">
-        <v>44826.723263888889</v>
+        <v>44826.7232638889</v>
       </c>
       <c r="T10" s="1">
-        <v>45180.683761574073</v>
+        <v>45180.6837615741</v>
       </c>
       <c r="V10">
         <v>0</v>
@@ -2048,13 +2657,13 @@
     </row>
     <row r="11" spans="1:22">
       <c r="A11" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D11" t="s">
-        <v>313</v>
+        <v>55</v>
       </c>
       <c r="E11" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -2093,10 +2702,10 @@
         <v>10</v>
       </c>
       <c r="S11" s="1">
-        <v>44838.877025462964</v>
+        <v>44838.877025463</v>
       </c>
       <c r="T11" s="1">
-        <v>45181.630150462966</v>
+        <v>45181.630150463</v>
       </c>
       <c r="V11">
         <v>0</v>
@@ -2104,16 +2713,16 @@
     </row>
     <row r="12" spans="1:22">
       <c r="A12" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="B12" t="s">
-        <v>332</v>
+        <v>58</v>
       </c>
       <c r="D12" t="s">
         <v>25</v>
       </c>
       <c r="E12" t="s">
-        <v>333</v>
+        <v>59</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -2149,10 +2758,10 @@
         <v>13</v>
       </c>
       <c r="S12" s="1">
-        <v>44862.895787037036</v>
+        <v>44862.895787037</v>
       </c>
       <c r="T12" s="1">
-        <v>45204.15283564815</v>
+        <v>45204.1528356482</v>
       </c>
       <c r="V12">
         <v>0</v>
@@ -2160,13 +2769,13 @@
     </row>
     <row r="13" spans="1:22">
       <c r="A13" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="D13" t="s">
-        <v>314</v>
+        <v>61</v>
       </c>
       <c r="E13" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -2205,10 +2814,10 @@
         <v>14</v>
       </c>
       <c r="S13" s="1">
-        <v>44864.733217592591</v>
+        <v>44864.7332175926</v>
       </c>
       <c r="T13" s="1">
-        <v>44864.733217592591</v>
+        <v>44864.7332175926</v>
       </c>
       <c r="V13">
         <v>0</v>
@@ -2216,13 +2825,13 @@
     </row>
     <row r="14" spans="1:22">
       <c r="A14" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="D14" t="s">
-        <v>315</v>
+        <v>64</v>
       </c>
       <c r="E14" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -2261,10 +2870,10 @@
         <v>15</v>
       </c>
       <c r="S14" s="1">
-        <v>44862.899155092593</v>
+        <v>44862.8991550926</v>
       </c>
       <c r="T14" s="1">
-        <v>44862.900057870371</v>
+        <v>44862.9000578704</v>
       </c>
       <c r="V14">
         <v>0</v>
@@ -2272,13 +2881,13 @@
     </row>
     <row r="15" spans="1:22">
       <c r="A15" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="D15" t="s">
-        <v>316</v>
+        <v>67</v>
       </c>
       <c r="E15" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -2317,10 +2926,10 @@
         <v>16</v>
       </c>
       <c r="S15" s="1">
-        <v>44862.925173611104</v>
+        <v>44862.9251736111</v>
       </c>
       <c r="T15" s="1">
-        <v>44863.569282407407</v>
+        <v>44863.5692824074</v>
       </c>
       <c r="V15">
         <v>0</v>
@@ -2328,7 +2937,7 @@
     </row>
     <row r="16" spans="1:22">
       <c r="A16" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="F16">
         <v>0</v>
@@ -2340,13 +2949,13 @@
         <v>0</v>
       </c>
       <c r="I16" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="J16">
         <v>7</v>
       </c>
       <c r="K16" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -2370,10 +2979,10 @@
         <v>17</v>
       </c>
       <c r="S16" s="1">
-        <v>44883.598217592589</v>
+        <v>44883.5982175926</v>
       </c>
       <c r="T16" s="1">
-        <v>44883.604062500002</v>
+        <v>44883.6040625</v>
       </c>
       <c r="V16">
         <v>0</v>
@@ -2381,7 +2990,7 @@
     </row>
     <row r="17" spans="1:22">
       <c r="A17" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -2393,13 +3002,13 @@
         <v>1</v>
       </c>
       <c r="I17" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="J17">
         <v>7</v>
       </c>
       <c r="K17" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="L17">
         <v>0</v>
@@ -2423,10 +3032,10 @@
         <v>18</v>
       </c>
       <c r="S17" s="1">
-        <v>44883.641030092593</v>
+        <v>44883.6410300926</v>
       </c>
       <c r="T17" s="1">
-        <v>44883.641030092593</v>
+        <v>44883.6410300926</v>
       </c>
       <c r="V17">
         <v>0</v>
@@ -2434,7 +3043,7 @@
     </row>
     <row r="18" spans="1:22">
       <c r="A18" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -2446,13 +3055,13 @@
         <v>2</v>
       </c>
       <c r="I18" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="J18">
         <v>7</v>
       </c>
       <c r="K18" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="L18">
         <v>0</v>
@@ -2476,10 +3085,10 @@
         <v>19</v>
       </c>
       <c r="S18" s="1">
-        <v>44883.641284722224</v>
+        <v>44883.6412847222</v>
       </c>
       <c r="T18" s="1">
-        <v>44883.641284722224</v>
+        <v>44883.6412847222</v>
       </c>
       <c r="V18">
         <v>0</v>
@@ -2487,7 +3096,7 @@
     </row>
     <row r="19" spans="1:22">
       <c r="A19" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -2499,13 +3108,13 @@
         <v>0</v>
       </c>
       <c r="I19" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="J19">
         <v>8</v>
       </c>
       <c r="K19" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="L19">
         <v>0</v>
@@ -2529,10 +3138,10 @@
         <v>20</v>
       </c>
       <c r="S19" s="1">
-        <v>44883.633275462969</v>
+        <v>44883.633275463</v>
       </c>
       <c r="T19" s="1">
-        <v>44883.633275462969</v>
+        <v>44883.633275463</v>
       </c>
       <c r="V19">
         <v>0</v>
@@ -2540,7 +3149,7 @@
     </row>
     <row r="20" spans="1:22">
       <c r="A20" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -2552,13 +3161,13 @@
         <v>1</v>
       </c>
       <c r="I20" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="J20">
         <v>8</v>
       </c>
       <c r="K20" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="L20">
         <v>0</v>
@@ -2582,10 +3191,10 @@
         <v>21</v>
       </c>
       <c r="S20" s="1">
-        <v>44883.64162037037</v>
+        <v>44883.6416203704</v>
       </c>
       <c r="T20" s="1">
-        <v>44883.64162037037</v>
+        <v>44883.6416203704</v>
       </c>
       <c r="V20">
         <v>0</v>
@@ -2593,7 +3202,7 @@
     </row>
     <row r="21" spans="1:22">
       <c r="A21" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -2605,13 +3214,13 @@
         <v>2</v>
       </c>
       <c r="I21" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="J21">
         <v>8</v>
       </c>
       <c r="K21" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="L21">
         <v>0</v>
@@ -2635,10 +3244,10 @@
         <v>22</v>
       </c>
       <c r="S21" s="1">
-        <v>44883.641793981486</v>
+        <v>44883.6417939815</v>
       </c>
       <c r="T21" s="1">
-        <v>45162.653738425921</v>
+        <v>45162.6537384259</v>
       </c>
       <c r="V21">
         <v>0</v>
@@ -2646,7 +3255,7 @@
     </row>
     <row r="22" spans="1:22">
       <c r="A22" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -2658,13 +3267,13 @@
         <v>0</v>
       </c>
       <c r="I22" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="J22">
         <v>9</v>
       </c>
       <c r="K22" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="L22">
         <v>0</v>
@@ -2688,10 +3297,10 @@
         <v>23</v>
       </c>
       <c r="S22" s="1">
-        <v>44883.643275462964</v>
+        <v>44883.643275463</v>
       </c>
       <c r="T22" s="1">
-        <v>44883.646527777775</v>
+        <v>44883.6465277778</v>
       </c>
       <c r="V22">
         <v>0</v>
@@ -2699,7 +3308,7 @@
     </row>
     <row r="23" spans="1:22">
       <c r="A23" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="F23">
         <v>0</v>
@@ -2711,13 +3320,13 @@
         <v>1</v>
       </c>
       <c r="I23" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="J23">
         <v>9</v>
       </c>
       <c r="K23" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="L23">
         <v>0</v>
@@ -2741,10 +3350,10 @@
         <v>24</v>
       </c>
       <c r="S23" s="1">
-        <v>44883.643530092595</v>
+        <v>44883.6435300926</v>
       </c>
       <c r="T23" s="1">
-        <v>44883.643530092595</v>
+        <v>44883.6435300926</v>
       </c>
       <c r="V23">
         <v>0</v>
@@ -2752,7 +3361,7 @@
     </row>
     <row r="24" spans="1:22">
       <c r="A24" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="F24">
         <v>0</v>
@@ -2764,13 +3373,13 @@
         <v>2</v>
       </c>
       <c r="I24" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="J24">
         <v>9</v>
       </c>
       <c r="K24" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="L24">
         <v>0</v>
@@ -2794,10 +3403,10 @@
         <v>25</v>
       </c>
       <c r="S24" s="1">
-        <v>44883.643819444449</v>
+        <v>44883.6438194444</v>
       </c>
       <c r="T24" s="1">
-        <v>44883.643819444449</v>
+        <v>44883.6438194444</v>
       </c>
       <c r="V24">
         <v>0</v>
@@ -2805,7 +3414,7 @@
     </row>
     <row r="25" spans="1:22">
       <c r="A25" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -2817,13 +3426,13 @@
         <v>3</v>
       </c>
       <c r="I25" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="J25">
         <v>9</v>
       </c>
       <c r="K25" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="L25">
         <v>0</v>
@@ -2847,10 +3456,10 @@
         <v>26</v>
       </c>
       <c r="S25" s="1">
-        <v>44883.644166666672</v>
+        <v>44883.6441666667</v>
       </c>
       <c r="T25" s="1">
-        <v>44883.644166666672</v>
+        <v>44883.6441666667</v>
       </c>
       <c r="V25">
         <v>0</v>
@@ -2858,7 +3467,7 @@
     </row>
     <row r="26" spans="1:22">
       <c r="A26" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="F26">
         <v>0</v>
@@ -2870,13 +3479,13 @@
         <v>4</v>
       </c>
       <c r="I26" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="J26">
         <v>9</v>
       </c>
       <c r="K26" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="L26">
         <v>0</v>
@@ -2900,10 +3509,10 @@
         <v>27</v>
       </c>
       <c r="S26" s="1">
-        <v>44883.64438657408</v>
+        <v>44883.6443865741</v>
       </c>
       <c r="T26" s="1">
-        <v>44883.64438657408</v>
+        <v>44883.6443865741</v>
       </c>
       <c r="V26">
         <v>0</v>
@@ -2911,7 +3520,7 @@
     </row>
     <row r="27" spans="1:22">
       <c r="A27" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="F27">
         <v>0</v>
@@ -2923,13 +3532,13 @@
         <v>5</v>
       </c>
       <c r="I27" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="J27">
         <v>9</v>
       </c>
       <c r="K27" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="L27">
         <v>0</v>
@@ -2953,10 +3562,10 @@
         <v>28</v>
       </c>
       <c r="S27" s="1">
-        <v>44883.644884259258</v>
+        <v>44883.6448842593</v>
       </c>
       <c r="T27" s="1">
-        <v>44883.644884259258</v>
+        <v>44883.6448842593</v>
       </c>
       <c r="V27">
         <v>0</v>
@@ -2964,16 +3573,16 @@
     </row>
     <row r="28" spans="1:22">
       <c r="A28" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="B28" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="D28" t="s">
         <v>25</v>
       </c>
       <c r="E28" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="F28">
         <v>0</v>
@@ -3009,10 +3618,10 @@
         <v>38</v>
       </c>
       <c r="S28" s="1">
-        <v>44973.689618055556</v>
+        <v>44973.6896180556</v>
       </c>
       <c r="T28" s="1">
-        <v>44973.690972222219</v>
+        <v>44973.6909722222</v>
       </c>
       <c r="V28">
         <v>0</v>
@@ -3020,13 +3629,13 @@
     </row>
     <row r="29" spans="1:22">
       <c r="A29" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="D29" t="s">
-        <v>317</v>
+        <v>98</v>
       </c>
       <c r="E29" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="F29">
         <v>0</v>
@@ -3065,10 +3674,10 @@
         <v>39</v>
       </c>
       <c r="S29" s="1">
-        <v>44973.690277777772</v>
+        <v>44973.6902777778</v>
       </c>
       <c r="T29" s="1">
-        <v>45180.522291666668</v>
+        <v>45180.5222916667</v>
       </c>
       <c r="V29">
         <v>0</v>
@@ -3076,13 +3685,13 @@
     </row>
     <row r="30" spans="1:22">
       <c r="A30" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="D30" t="s">
-        <v>318</v>
+        <v>101</v>
       </c>
       <c r="E30" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="F30">
         <v>0</v>
@@ -3121,10 +3730,10 @@
         <v>40</v>
       </c>
       <c r="S30" s="1">
-        <v>44973.717280092591</v>
+        <v>44973.7172800926</v>
       </c>
       <c r="T30" s="1">
-        <v>45180.522523148145</v>
+        <v>45180.5225231481</v>
       </c>
       <c r="V30">
         <v>0</v>
@@ -3132,13 +3741,13 @@
     </row>
     <row r="31" spans="1:22">
       <c r="A31" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="D31" t="s">
-        <v>319</v>
+        <v>104</v>
       </c>
       <c r="E31" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="F31">
         <v>0</v>
@@ -3177,10 +3786,10 @@
         <v>42</v>
       </c>
       <c r="S31" s="1">
-        <v>44978.987083333333</v>
+        <v>44978.9870833333</v>
       </c>
       <c r="T31" s="1">
-        <v>45180.522719907407</v>
+        <v>45180.5227199074</v>
       </c>
       <c r="V31">
         <v>0</v>
@@ -3188,16 +3797,16 @@
     </row>
     <row r="32" spans="1:22">
       <c r="A32" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="B32" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="C32" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="E32" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="F32">
         <v>0</v>
@@ -3233,10 +3842,10 @@
         <v>68</v>
       </c>
       <c r="S32" s="1">
-        <v>44889.630127314813</v>
+        <v>44889.6301273148</v>
       </c>
       <c r="T32" s="1">
-        <v>44889.641284722224</v>
+        <v>44889.6412847222</v>
       </c>
       <c r="V32">
         <v>0</v>
@@ -3244,13 +3853,13 @@
     </row>
     <row r="33" spans="1:22">
       <c r="A33" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="D33" t="s">
-        <v>320</v>
+        <v>111</v>
       </c>
       <c r="E33" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="F33">
         <v>0</v>
@@ -3289,10 +3898,10 @@
         <v>69</v>
       </c>
       <c r="S33" s="1">
-        <v>44889.630659722228</v>
+        <v>44889.6306597222</v>
       </c>
       <c r="T33" s="1">
-        <v>45187.411562499998</v>
+        <v>45187.4115625</v>
       </c>
       <c r="V33">
         <v>0</v>
@@ -3300,13 +3909,13 @@
     </row>
     <row r="34" spans="1:22">
       <c r="A34" t="s">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="D34" t="s">
-        <v>321</v>
+        <v>114</v>
       </c>
       <c r="E34" t="s">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="F34">
         <v>0</v>
@@ -3345,10 +3954,10 @@
         <v>73</v>
       </c>
       <c r="S34" s="1">
-        <v>45102.614305555559</v>
+        <v>45102.6143055556</v>
       </c>
       <c r="T34" s="1">
-        <v>45187.657708333332</v>
+        <v>45187.6577083333</v>
       </c>
       <c r="V34">
         <v>0</v>
@@ -3356,13 +3965,13 @@
     </row>
     <row r="35" spans="1:22">
       <c r="A35" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="D35" t="s">
-        <v>322</v>
+        <v>117</v>
       </c>
       <c r="E35" t="s">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="F35">
         <v>0</v>
@@ -3401,10 +4010,10 @@
         <v>74</v>
       </c>
       <c r="S35" s="1">
-        <v>45105.454143518517</v>
+        <v>45105.4541435185</v>
       </c>
       <c r="T35" s="1">
-        <v>45182.723865740743</v>
+        <v>45182.7238657407</v>
       </c>
       <c r="V35">
         <v>0</v>
@@ -3412,7 +4021,7 @@
     </row>
     <row r="36" spans="1:22">
       <c r="A36" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="F36">
         <v>0</v>
@@ -3424,13 +4033,13 @@
         <v>3</v>
       </c>
       <c r="I36" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="J36">
         <v>7</v>
       </c>
       <c r="K36" t="s">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="L36">
         <v>0</v>
@@ -3454,10 +4063,10 @@
         <v>76</v>
       </c>
       <c r="S36" s="1">
-        <v>45162.653043981481</v>
+        <v>45162.6530439815</v>
       </c>
       <c r="T36" s="1">
-        <v>45162.653043981481</v>
+        <v>45162.6530439815</v>
       </c>
       <c r="V36">
         <v>0</v>
@@ -3465,7 +4074,7 @@
     </row>
     <row r="37" spans="1:22">
       <c r="A37" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="F37">
         <v>0</v>
@@ -3477,13 +4086,13 @@
         <v>3</v>
       </c>
       <c r="I37" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="J37">
         <v>8</v>
       </c>
       <c r="K37" t="s">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="L37">
         <v>0</v>
@@ -3507,10 +4116,10 @@
         <v>77</v>
       </c>
       <c r="S37" s="1">
-        <v>45162.653321759266</v>
+        <v>45162.6533217593</v>
       </c>
       <c r="T37" s="1">
-        <v>45162.653321759266</v>
+        <v>45162.6533217593</v>
       </c>
       <c r="V37">
         <v>0</v>
@@ -3518,7 +4127,7 @@
     </row>
     <row r="38" spans="1:22">
       <c r="A38" t="s">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="F38">
         <v>0</v>
@@ -3530,13 +4139,13 @@
         <v>6</v>
       </c>
       <c r="I38" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="J38">
         <v>9</v>
       </c>
       <c r="K38" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="L38">
         <v>0</v>
@@ -3560,10 +4169,10 @@
         <v>78</v>
       </c>
       <c r="S38" s="1">
-        <v>45162.653657407405</v>
+        <v>45162.6536574074</v>
       </c>
       <c r="T38" s="1">
-        <v>45162.653657407405</v>
+        <v>45162.6536574074</v>
       </c>
       <c r="V38">
         <v>0</v>
@@ -3571,16 +4180,16 @@
     </row>
     <row r="39" spans="1:22">
       <c r="A39" t="s">
-        <v>108</v>
+        <v>124</v>
       </c>
       <c r="B39" t="s">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="D39" t="s">
         <v>25</v>
       </c>
       <c r="E39" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="F39">
         <v>0</v>
@@ -3616,10 +4225,10 @@
         <v>79</v>
       </c>
       <c r="S39" s="1">
-        <v>45163.58084490741</v>
+        <v>45163.5808449074</v>
       </c>
       <c r="T39" s="1">
-        <v>45163.58084490741</v>
+        <v>45163.5808449074</v>
       </c>
       <c r="V39">
         <v>0</v>
@@ -3627,13 +4236,13 @@
     </row>
     <row r="40" spans="1:22">
       <c r="A40" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="D40" t="s">
-        <v>323</v>
+        <v>128</v>
       </c>
       <c r="E40" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="F40">
         <v>0</v>
@@ -3672,10 +4281,10 @@
         <v>80</v>
       </c>
       <c r="S40" s="1">
-        <v>45163.581469907404</v>
+        <v>45163.5814699074</v>
       </c>
       <c r="T40" s="1">
-        <v>45183.466342592597</v>
+        <v>45183.4663425926</v>
       </c>
       <c r="V40">
         <v>0</v>
@@ -3683,13 +4292,13 @@
     </row>
     <row r="41" spans="1:22">
       <c r="A41" t="s">
-        <v>334</v>
+        <v>130</v>
       </c>
       <c r="D41" t="s">
-        <v>335</v>
+        <v>131</v>
       </c>
       <c r="E41" t="s">
-        <v>336</v>
+        <v>132</v>
       </c>
       <c r="F41">
         <v>0</v>
@@ -3728,34 +4337,35 @@
         <v>81</v>
       </c>
       <c r="S41" s="1">
-        <v>45278.950706018521</v>
+        <v>45278.9507060185</v>
       </c>
       <c r="T41" s="1">
-        <v>45278.950706018521</v>
+        <v>45278.9507060185</v>
       </c>
       <c r="V41">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:K8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="7"/>
   <cols>
     <col min="1" max="1" width="3.5703125" customWidth="1"/>
-    <col min="2" max="3" width="18.85546875" customWidth="1"/>
-    <col min="4" max="4" width="17.42578125" customWidth="1"/>
+    <col min="2" max="3" width="18.859375" customWidth="1"/>
+    <col min="4" max="4" width="17.4296875" customWidth="1"/>
     <col min="7" max="7" width="52.5703125" customWidth="1"/>
-    <col min="8" max="8" width="15.28515625" customWidth="1"/>
-    <col min="9" max="9" width="14.28515625" customWidth="1"/>
-    <col min="10" max="10" width="9.28515625" customWidth="1"/>
-    <col min="11" max="11" width="15.28515625" customWidth="1"/>
+    <col min="8" max="8" width="15.2890625" customWidth="1"/>
+    <col min="9" max="9" width="14.2890625" customWidth="1"/>
+    <col min="10" max="10" width="9.2890625" customWidth="1"/>
+    <col min="11" max="11" width="15.2890625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
@@ -3775,22 +4385,22 @@
         <v>21</v>
       </c>
       <c r="F1" t="s">
-        <v>292</v>
+        <v>324</v>
       </c>
       <c r="G1" t="s">
         <v>0</v>
       </c>
       <c r="H1" t="s">
-        <v>293</v>
+        <v>325</v>
       </c>
       <c r="I1" t="s">
-        <v>294</v>
+        <v>326</v>
       </c>
       <c r="J1" t="s">
-        <v>124</v>
+        <v>146</v>
       </c>
       <c r="K1" t="s">
-        <v>289</v>
+        <v>321</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -3798,10 +4408,10 @@
         <v>6</v>
       </c>
       <c r="B2" s="1">
-        <v>44984.657164351898</v>
+        <v>44984.6571643519</v>
       </c>
       <c r="C2" s="1">
-        <v>45142.737500000003</v>
+        <v>45142.7375</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -3810,10 +4420,10 @@
         <v>3</v>
       </c>
       <c r="G2" t="s">
-        <v>295</v>
+        <v>327</v>
       </c>
       <c r="H2" t="s">
-        <v>296</v>
+        <v>328</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -3830,7 +4440,7 @@
         <v>7</v>
       </c>
       <c r="B3" s="1">
-        <v>44984.657337962999</v>
+        <v>44984.657337963</v>
       </c>
       <c r="C3" s="1">
         <v>45142.7374305556</v>
@@ -3842,10 +4452,10 @@
         <v>3</v>
       </c>
       <c r="G3" t="s">
-        <v>297</v>
+        <v>329</v>
       </c>
       <c r="H3" t="s">
-        <v>298</v>
+        <v>330</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -3862,10 +4472,10 @@
         <v>8</v>
       </c>
       <c r="B4" s="1">
-        <v>44984.657453703701</v>
+        <v>44984.6574537037</v>
       </c>
       <c r="C4" s="1">
-        <v>45142.737453703703</v>
+        <v>45142.7374537037</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -3874,10 +4484,10 @@
         <v>3</v>
       </c>
       <c r="G4" t="s">
-        <v>299</v>
+        <v>331</v>
       </c>
       <c r="H4" t="s">
-        <v>300</v>
+        <v>332</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3894,10 +4504,10 @@
         <v>9</v>
       </c>
       <c r="B5" s="1">
-        <v>44984.657581018502</v>
+        <v>44984.6575810185</v>
       </c>
       <c r="C5" s="1">
-        <v>45142.737476851798</v>
+        <v>45142.7374768518</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -3906,10 +4516,10 @@
         <v>3</v>
       </c>
       <c r="G5" t="s">
-        <v>301</v>
+        <v>333</v>
       </c>
       <c r="H5" t="s">
-        <v>302</v>
+        <v>334</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -3926,10 +4536,10 @@
         <v>10</v>
       </c>
       <c r="B6" s="1">
-        <v>44984.657719907402</v>
+        <v>44984.6577199074</v>
       </c>
       <c r="C6" s="1">
-        <v>45141.021805555603</v>
+        <v>45141.0218055556</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -3938,10 +4548,10 @@
         <v>4</v>
       </c>
       <c r="G6" t="s">
-        <v>303</v>
+        <v>335</v>
       </c>
       <c r="H6" t="s">
-        <v>304</v>
+        <v>336</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -3958,10 +4568,10 @@
         <v>11</v>
       </c>
       <c r="B7" s="1">
-        <v>44984.657847222203</v>
+        <v>44984.6578472222</v>
       </c>
       <c r="C7" s="1">
-        <v>45129.748043981497</v>
+        <v>45129.7480439815</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -3970,10 +4580,10 @@
         <v>4</v>
       </c>
       <c r="G7" t="s">
-        <v>305</v>
+        <v>337</v>
       </c>
       <c r="H7" t="s">
-        <v>306</v>
+        <v>338</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -3993,7 +4603,7 @@
         <v>44984.657962963</v>
       </c>
       <c r="C8" s="1">
-        <v>45142.737407407403</v>
+        <v>45142.7374074074</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -4002,10 +4612,10 @@
         <v>4</v>
       </c>
       <c r="G8" t="s">
-        <v>307</v>
+        <v>339</v>
       </c>
       <c r="H8" t="s">
-        <v>308</v>
+        <v>340</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -4018,28 +4628,29 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{355349EC-D151-4041-BE71-35E0B9FED49F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:N2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="1" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="20.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.2890625" customWidth="1"/>
+    <col min="2" max="2" width="12.2890625" customWidth="1"/>
+    <col min="11" max="12" width="20.140625" customWidth="1"/>
+    <col min="13" max="13" width="17.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" t="s">
-        <v>113</v>
+        <v>133</v>
       </c>
       <c r="B1" t="s">
-        <v>324</v>
+        <v>341</v>
       </c>
       <c r="C1" t="s">
         <v>5</v>
@@ -4048,16 +4659,16 @@
         <v>7</v>
       </c>
       <c r="E1" t="s">
-        <v>115</v>
+        <v>135</v>
       </c>
       <c r="F1" t="s">
-        <v>325</v>
+        <v>342</v>
       </c>
       <c r="G1" t="s">
-        <v>326</v>
+        <v>343</v>
       </c>
       <c r="H1" t="s">
-        <v>327</v>
+        <v>142</v>
       </c>
       <c r="I1" t="s">
         <v>9</v>
@@ -4080,10 +4691,10 @@
     </row>
     <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>328</v>
+        <v>344</v>
       </c>
       <c r="B2" t="s">
-        <v>329</v>
+        <v>345</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -4095,32 +4706,33 @@
         <v>1</v>
       </c>
       <c r="K2" s="1">
-        <v>45278.952164351846</v>
+        <v>45278.9521643518</v>
       </c>
       <c r="L2" s="1">
-        <v>45281.748402777775</v>
+        <v>45281.7484027778</v>
       </c>
       <c r="N2">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0766066A-E4AE-420C-89ED-591352846793}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="1" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>330</v>
+        <v>346</v>
       </c>
       <c r="B1" t="s">
-        <v>331</v>
+        <v>347</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -4132,23 +4744,24 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="120" orientation="portrait" horizontalDpi="203" verticalDpi="203" r:id="rId1"/>
+  <pageSetup paperSize="120" orientation="portrait" horizontalDpi="203" verticalDpi="203"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:L2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="1"/>
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" t="s">
-        <v>113</v>
+        <v>133</v>
       </c>
       <c r="B1" t="s">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="C1" t="s">
         <v>5</v>
@@ -4157,10 +4770,10 @@
         <v>7</v>
       </c>
       <c r="E1" t="s">
-        <v>115</v>
+        <v>135</v>
       </c>
       <c r="F1" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="G1" t="s">
         <v>17</v>
@@ -4178,15 +4791,15 @@
         <v>21</v>
       </c>
       <c r="L1" t="s">
-        <v>337</v>
+        <v>137</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" t="s">
-        <v>117</v>
+        <v>138</v>
       </c>
       <c r="B2" t="s">
-        <v>118</v>
+        <v>139</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -4201,10 +4814,10 @@
         <v>1</v>
       </c>
       <c r="H2" s="1">
-        <v>44786.457152777773</v>
+        <v>44786.4571527778</v>
       </c>
       <c r="I2" s="1">
-        <v>44843.627476851849</v>
+        <v>44843.6274768518</v>
       </c>
       <c r="K2">
         <v>0</v>
@@ -4214,58 +4827,62 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:S2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="1"/>
+  <cols>
+    <col min="2" max="2" width="25.6484375" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:19">
       <c r="A1" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="B1" t="s">
-        <v>119</v>
+        <v>141</v>
       </c>
       <c r="C1" t="s">
-        <v>327</v>
+        <v>142</v>
       </c>
       <c r="D1" t="s">
-        <v>113</v>
+        <v>133</v>
       </c>
       <c r="E1" t="s">
-        <v>120</v>
+        <v>143</v>
       </c>
       <c r="F1" t="s">
-        <v>121</v>
+        <v>144</v>
       </c>
       <c r="G1" t="s">
-        <v>123</v>
+        <v>145</v>
       </c>
       <c r="H1" t="s">
-        <v>124</v>
+        <v>146</v>
       </c>
       <c r="I1" t="s">
-        <v>125</v>
+        <v>147</v>
       </c>
       <c r="J1" t="s">
-        <v>126</v>
+        <v>148</v>
       </c>
       <c r="K1" t="s">
-        <v>127</v>
+        <v>149</v>
       </c>
       <c r="L1" t="s">
-        <v>128</v>
+        <v>150</v>
       </c>
       <c r="M1" t="s">
-        <v>338</v>
+        <v>151</v>
       </c>
       <c r="N1" t="s">
-        <v>339</v>
+        <v>152</v>
       </c>
       <c r="O1" t="s">
         <v>17</v>
@@ -4284,17 +4901,17 @@
       </c>
     </row>
     <row r="2" spans="1:19">
-      <c r="B2" t="s">
-        <v>129</v>
+      <c r="B2">
+        <v>17302869369</v>
       </c>
       <c r="D2" t="s">
-        <v>130</v>
+        <v>153</v>
       </c>
       <c r="E2" t="s">
-        <v>118</v>
+        <v>139</v>
       </c>
       <c r="F2" t="s">
-        <v>131</v>
+        <v>154</v>
       </c>
       <c r="G2" t="s">
         <v>38</v>
@@ -4306,10 +4923,10 @@
         <v>1</v>
       </c>
       <c r="J2" t="s">
-        <v>132</v>
+        <v>155</v>
       </c>
       <c r="K2" s="1">
-        <v>45311.463958333341</v>
+        <v>45311.4639583333</v>
       </c>
       <c r="L2">
         <v>1</v>
@@ -4321,32 +4938,33 @@
         <v>1</v>
       </c>
       <c r="P2" s="1">
-        <v>44784.845185185193</v>
+        <v>44784.8451851852</v>
       </c>
       <c r="Q2" s="1">
-        <v>45311.463923611118</v>
+        <v>45311.4639236111</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="1" outlineLevelCol="1"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" ht="17" spans="1:2">
       <c r="A1" t="s">
-        <v>133</v>
+        <v>156</v>
       </c>
       <c r="B1" t="s">
-        <v>134</v>
+        <v>157</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -4358,29 +4976,30 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:I7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="6"/>
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" t="s">
-        <v>135</v>
+        <v>158</v>
       </c>
       <c r="B1" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
       <c r="C1" t="s">
         <v>5</v>
       </c>
       <c r="D1" t="s">
-        <v>137</v>
+        <v>160</v>
       </c>
       <c r="E1" t="s">
         <v>17</v>
@@ -4400,10 +5019,10 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>138</v>
+        <v>161</v>
       </c>
       <c r="B2" t="s">
-        <v>139</v>
+        <v>162</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -4412,10 +5031,10 @@
         <v>1</v>
       </c>
       <c r="F2" s="1">
-        <v>44839.919247685182</v>
+        <v>44839.9192476852</v>
       </c>
       <c r="G2" s="1">
-        <v>44842.58143518518</v>
+        <v>44842.5814351852</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -4423,10 +5042,10 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>140</v>
+        <v>163</v>
       </c>
       <c r="B3" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -4435,10 +5054,10 @@
         <v>2</v>
       </c>
       <c r="F3" s="1">
-        <v>44842.581620370365</v>
+        <v>44842.5816203704</v>
       </c>
       <c r="G3" s="1">
-        <v>44842.581620370365</v>
+        <v>44842.5816203704</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4446,10 +5065,10 @@
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>142</v>
+        <v>165</v>
       </c>
       <c r="B4" t="s">
-        <v>143</v>
+        <v>166</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -4458,10 +5077,10 @@
         <v>3</v>
       </c>
       <c r="F4" s="1">
-        <v>44898.991770833338</v>
+        <v>44898.9917708333</v>
       </c>
       <c r="G4" s="1">
-        <v>44898.991770833338</v>
+        <v>44898.9917708333</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4469,10 +5088,10 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>144</v>
+        <v>167</v>
       </c>
       <c r="B5" t="s">
-        <v>145</v>
+        <v>168</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -4481,10 +5100,10 @@
         <v>4</v>
       </c>
       <c r="F5" s="1">
-        <v>44898.992488425931</v>
+        <v>44898.9924884259</v>
       </c>
       <c r="G5" s="1">
-        <v>44898.992488425931</v>
+        <v>44898.9924884259</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4492,25 +5111,25 @@
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>146</v>
+        <v>169</v>
       </c>
       <c r="B6" t="s">
-        <v>147</v>
+        <v>170</v>
       </c>
       <c r="C6">
         <v>0</v>
       </c>
       <c r="D6" t="s">
-        <v>148</v>
+        <v>171</v>
       </c>
       <c r="E6">
         <v>5</v>
       </c>
       <c r="F6" s="1">
-        <v>45102.705092592594</v>
+        <v>45102.7050925926</v>
       </c>
       <c r="G6" s="1">
-        <v>45107.39130787037</v>
+        <v>45107.3913078704</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4518,10 +5137,10 @@
     </row>
     <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>340</v>
+        <v>172</v>
       </c>
       <c r="B7" t="s">
-        <v>341</v>
+        <v>173</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -4530,47 +5149,48 @@
         <v>6</v>
       </c>
       <c r="F7" s="1">
-        <v>45281.775648148148</v>
+        <v>45281.7756481481</v>
       </c>
       <c r="G7" s="1">
-        <v>45281.775648148148</v>
+        <v>45281.7756481481</v>
       </c>
       <c r="I7">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:L19"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" t="s">
-        <v>151</v>
+        <v>174</v>
       </c>
       <c r="B1" t="s">
-        <v>152</v>
+        <v>175</v>
       </c>
       <c r="C1" t="s">
         <v>5</v>
       </c>
       <c r="D1" t="s">
-        <v>149</v>
+        <v>176</v>
       </c>
       <c r="E1" t="s">
         <v>7</v>
       </c>
       <c r="F1" t="s">
-        <v>150</v>
+        <v>177</v>
       </c>
       <c r="G1" t="s">
-        <v>137</v>
+        <v>160</v>
       </c>
       <c r="H1" t="s">
         <v>17</v>
@@ -4590,7 +5210,7 @@
     </row>
     <row r="2" spans="1:12">
       <c r="A2" t="s">
-        <v>153</v>
+        <v>178</v>
       </c>
       <c r="B2" t="s">
         <v>27</v>
@@ -4611,10 +5231,10 @@
         <v>2</v>
       </c>
       <c r="I2" s="1">
-        <v>44841.505358796298</v>
+        <v>44841.5053587963</v>
       </c>
       <c r="J2" s="1">
-        <v>44841.505578703705</v>
+        <v>44841.5055787037</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -4622,7 +5242,7 @@
     </row>
     <row r="3" spans="1:12">
       <c r="A3" t="s">
-        <v>154</v>
+        <v>179</v>
       </c>
       <c r="B3" t="s">
         <v>38</v>
@@ -4643,10 +5263,10 @@
         <v>4</v>
       </c>
       <c r="I3" s="1">
-        <v>44842.580231481479</v>
+        <v>44842.5802314815</v>
       </c>
       <c r="J3" s="1">
-        <v>44842.580231481479</v>
+        <v>44842.5802314815</v>
       </c>
       <c r="L3">
         <v>0</v>
@@ -4654,7 +5274,7 @@
     </row>
     <row r="4" spans="1:12">
       <c r="A4" t="s">
-        <v>155</v>
+        <v>180</v>
       </c>
       <c r="B4" t="s">
         <v>27</v>
@@ -4675,10 +5295,10 @@
         <v>5</v>
       </c>
       <c r="I4" s="1">
-        <v>44842.586979166663</v>
+        <v>44842.5869791667</v>
       </c>
       <c r="J4" s="1">
-        <v>44842.587245370371</v>
+        <v>44842.5872453704</v>
       </c>
       <c r="L4">
         <v>0</v>
@@ -4686,7 +5306,7 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" t="s">
-        <v>156</v>
+        <v>181</v>
       </c>
       <c r="B5" t="s">
         <v>38</v>
@@ -4707,10 +5327,10 @@
         <v>6</v>
       </c>
       <c r="I5" s="1">
-        <v>44842.587083333332</v>
+        <v>44842.5870833333</v>
       </c>
       <c r="J5" s="1">
-        <v>44842.587083333332</v>
+        <v>44842.5870833333</v>
       </c>
       <c r="L5">
         <v>0</v>
@@ -4718,10 +5338,10 @@
     </row>
     <row r="6" spans="1:12">
       <c r="A6" t="s">
-        <v>157</v>
+        <v>182</v>
       </c>
       <c r="B6" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -4739,10 +5359,10 @@
         <v>7</v>
       </c>
       <c r="I6" s="1">
-        <v>44842.587175925924</v>
+        <v>44842.5871759259</v>
       </c>
       <c r="J6" s="1">
-        <v>44842.587175925924</v>
+        <v>44842.5871759259</v>
       </c>
       <c r="L6">
         <v>0</v>
@@ -4750,7 +5370,7 @@
     </row>
     <row r="7" spans="1:12">
       <c r="A7" t="s">
-        <v>158</v>
+        <v>183</v>
       </c>
       <c r="B7" t="s">
         <v>27</v>
@@ -4771,10 +5391,10 @@
         <v>8</v>
       </c>
       <c r="I7" s="1">
-        <v>44898.992048611115</v>
+        <v>44898.9920486111</v>
       </c>
       <c r="J7" s="1">
-        <v>44898.992048611115</v>
+        <v>44898.9920486111</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -4782,7 +5402,7 @@
     </row>
     <row r="8" spans="1:12">
       <c r="A8" t="s">
-        <v>159</v>
+        <v>184</v>
       </c>
       <c r="B8" t="s">
         <v>38</v>
@@ -4803,10 +5423,10 @@
         <v>9</v>
       </c>
       <c r="I8" s="1">
-        <v>44898.992210648154</v>
+        <v>44898.9922106482</v>
       </c>
       <c r="J8" s="1">
-        <v>44898.992210648154</v>
+        <v>44898.9922106482</v>
       </c>
       <c r="L8">
         <v>0</v>
@@ -4814,7 +5434,7 @@
     </row>
     <row r="9" spans="1:12">
       <c r="A9" t="s">
-        <v>160</v>
+        <v>185</v>
       </c>
       <c r="B9" t="s">
         <v>27</v>
@@ -4835,10 +5455,10 @@
         <v>10</v>
       </c>
       <c r="I9" s="1">
-        <v>44898.992638888893</v>
+        <v>44898.9926388889</v>
       </c>
       <c r="J9" s="1">
-        <v>44898.992638888893</v>
+        <v>44898.9926388889</v>
       </c>
       <c r="L9">
         <v>0</v>
@@ -4846,7 +5466,7 @@
     </row>
     <row r="10" spans="1:12">
       <c r="A10" t="s">
-        <v>161</v>
+        <v>186</v>
       </c>
       <c r="B10" t="s">
         <v>38</v>
@@ -4867,10 +5487,10 @@
         <v>11</v>
       </c>
       <c r="I10" s="1">
-        <v>44898.992835648154</v>
+        <v>44898.9928356482</v>
       </c>
       <c r="J10" s="1">
-        <v>44898.992835648154</v>
+        <v>44898.9928356482</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -4878,10 +5498,10 @@
     </row>
     <row r="11" spans="1:12">
       <c r="A11" t="s">
-        <v>162</v>
+        <v>187</v>
       </c>
       <c r="B11" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -4899,10 +5519,10 @@
         <v>12</v>
       </c>
       <c r="I11" s="1">
-        <v>44980.950659722221</v>
+        <v>44980.9506597222</v>
       </c>
       <c r="J11" s="1">
-        <v>44980.953773148147</v>
+        <v>44980.9537731481</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -4910,10 +5530,10 @@
     </row>
     <row r="12" spans="1:12">
       <c r="A12" t="s">
-        <v>163</v>
+        <v>188</v>
       </c>
       <c r="B12" t="s">
-        <v>164</v>
+        <v>189</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -4931,10 +5551,10 @@
         <v>14</v>
       </c>
       <c r="I12" s="1">
-        <v>45102.705671296295</v>
+        <v>45102.7056712963</v>
       </c>
       <c r="J12" s="1">
-        <v>45103.66128472222</v>
+        <v>45103.6612847222</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -4942,10 +5562,10 @@
     </row>
     <row r="13" spans="1:12">
       <c r="A13" t="s">
-        <v>165</v>
+        <v>190</v>
       </c>
       <c r="B13" t="s">
-        <v>166</v>
+        <v>191</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -4963,10 +5583,10 @@
         <v>15</v>
       </c>
       <c r="I13" s="1">
-        <v>45102.706574074073</v>
+        <v>45102.7065740741</v>
       </c>
       <c r="J13" s="1">
-        <v>45102.706574074073</v>
+        <v>45102.7065740741</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -4974,10 +5594,10 @@
     </row>
     <row r="14" spans="1:12">
       <c r="A14" t="s">
-        <v>167</v>
+        <v>192</v>
       </c>
       <c r="B14" t="s">
-        <v>168</v>
+        <v>193</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -4995,10 +5615,10 @@
         <v>16</v>
       </c>
       <c r="I14" s="1">
-        <v>45102.706724537034</v>
+        <v>45102.706724537</v>
       </c>
       <c r="J14" s="1">
-        <v>45103.661400462966</v>
+        <v>45103.661400463</v>
       </c>
       <c r="L14">
         <v>0</v>
@@ -5006,7 +5626,7 @@
     </row>
     <row r="15" spans="1:12">
       <c r="A15" t="s">
-        <v>342</v>
+        <v>194</v>
       </c>
       <c r="B15" t="s">
         <v>27</v>
@@ -5027,10 +5647,10 @@
         <v>17</v>
       </c>
       <c r="I15" s="1">
-        <v>45281.777569444443</v>
+        <v>45281.7775694444</v>
       </c>
       <c r="J15" s="1">
-        <v>45257.65048611111</v>
+        <v>45257.6504861111</v>
       </c>
       <c r="L15">
         <v>0</v>
@@ -5038,7 +5658,7 @@
     </row>
     <row r="16" spans="1:12">
       <c r="A16" t="s">
-        <v>343</v>
+        <v>195</v>
       </c>
       <c r="B16" t="s">
         <v>38</v>
@@ -5059,10 +5679,10 @@
         <v>18</v>
       </c>
       <c r="I16" s="1">
-        <v>45281.777731481481</v>
+        <v>45281.7777314815</v>
       </c>
       <c r="J16" s="1">
-        <v>45257.651412037034</v>
+        <v>45257.651412037</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -5070,10 +5690,10 @@
     </row>
     <row r="17" spans="1:12">
       <c r="A17" t="s">
-        <v>344</v>
+        <v>196</v>
       </c>
       <c r="B17" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -5091,10 +5711,10 @@
         <v>19</v>
       </c>
       <c r="I17" s="1">
-        <v>45281.777847222227</v>
+        <v>45281.7778472222</v>
       </c>
       <c r="J17" s="1">
-        <v>45257.651539351849</v>
+        <v>45257.6515393518</v>
       </c>
       <c r="L17">
         <v>0</v>
@@ -5102,10 +5722,10 @@
     </row>
     <row r="18" spans="1:12">
       <c r="A18" t="s">
-        <v>345</v>
+        <v>197</v>
       </c>
       <c r="B18" t="s">
-        <v>346</v>
+        <v>198</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -5123,10 +5743,10 @@
         <v>20</v>
       </c>
       <c r="I18" s="1">
-        <v>45281.777951388889</v>
+        <v>45281.7779513889</v>
       </c>
       <c r="J18" s="1">
-        <v>45257.651597222219</v>
+        <v>45257.6515972222</v>
       </c>
       <c r="L18">
         <v>0</v>
@@ -5134,10 +5754,10 @@
     </row>
     <row r="19" spans="1:12">
       <c r="A19" t="s">
-        <v>347</v>
+        <v>199</v>
       </c>
       <c r="B19" t="s">
-        <v>348</v>
+        <v>200</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -5155,33 +5775,34 @@
         <v>21</v>
       </c>
       <c r="I19" s="1">
-        <v>45281.778078703705</v>
+        <v>45281.7780787037</v>
       </c>
       <c r="J19" s="1">
-        <v>45257.651655092588</v>
+        <v>45257.6516550926</v>
       </c>
       <c r="L19">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:K11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="2" max="2" width="20" customWidth="1"/>
     <col min="3" max="3" width="20.140625" customWidth="1"/>
-    <col min="4" max="4" width="17.42578125" customWidth="1"/>
+    <col min="4" max="4" width="17.4296875" customWidth="1"/>
     <col min="5" max="5" width="12.7109375" customWidth="1"/>
-    <col min="6" max="6" width="10.28515625" customWidth="1"/>
+    <col min="6" max="6" width="10.2890625" customWidth="1"/>
     <col min="8" max="8" width="8.140625" customWidth="1"/>
-    <col min="9" max="9" width="17.85546875" customWidth="1"/>
+    <col min="9" max="9" width="17.859375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
@@ -5201,16 +5822,16 @@
         <v>0</v>
       </c>
       <c r="F1" t="s">
-        <v>169</v>
+        <v>201</v>
       </c>
       <c r="G1" t="s">
         <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>170</v>
+        <v>202</v>
       </c>
       <c r="I1" t="s">
-        <v>171</v>
+        <v>203</v>
       </c>
       <c r="J1" t="s">
         <v>5</v>
@@ -5224,25 +5845,25 @@
         <v>1</v>
       </c>
       <c r="B2" s="1">
-        <v>44865.828298611101</v>
+        <v>44865.8282986111</v>
       </c>
       <c r="C2" s="1">
-        <v>44865.828298611101</v>
+        <v>44865.8282986111</v>
       </c>
       <c r="E2" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="F2" t="s">
-        <v>172</v>
+        <v>204</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>173</v>
+        <v>205</v>
       </c>
       <c r="I2" t="s">
-        <v>174</v>
+        <v>206</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -5256,25 +5877,25 @@
         <v>2</v>
       </c>
       <c r="B3" s="1">
-        <v>44865.828298611101</v>
+        <v>44865.8282986111</v>
       </c>
       <c r="C3" s="1">
-        <v>44865.828298611101</v>
+        <v>44865.8282986111</v>
       </c>
       <c r="E3" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="F3" t="s">
-        <v>175</v>
+        <v>207</v>
       </c>
       <c r="G3">
         <v>1</v>
       </c>
       <c r="H3" t="s">
-        <v>173</v>
+        <v>205</v>
       </c>
       <c r="I3" t="s">
-        <v>176</v>
+        <v>208</v>
       </c>
       <c r="J3">
         <v>1</v>
@@ -5288,25 +5909,25 @@
         <v>3</v>
       </c>
       <c r="B4" s="1">
-        <v>44865.828298611101</v>
+        <v>44865.8282986111</v>
       </c>
       <c r="C4" s="1">
-        <v>44865.828298611101</v>
+        <v>44865.8282986111</v>
       </c>
       <c r="E4" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="F4" t="s">
-        <v>177</v>
+        <v>209</v>
       </c>
       <c r="G4">
         <v>1</v>
       </c>
       <c r="H4" t="s">
-        <v>173</v>
+        <v>205</v>
       </c>
       <c r="I4" t="s">
-        <v>178</v>
+        <v>210</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -5320,25 +5941,25 @@
         <v>4</v>
       </c>
       <c r="B5" s="1">
-        <v>44865.828298611101</v>
+        <v>44865.8282986111</v>
       </c>
       <c r="C5" s="1">
-        <v>44865.828298611101</v>
+        <v>44865.8282986111</v>
       </c>
       <c r="E5" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="F5" t="s">
-        <v>179</v>
+        <v>211</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>173</v>
+        <v>205</v>
       </c>
       <c r="I5" t="s">
-        <v>180</v>
+        <v>212</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -5352,25 +5973,25 @@
         <v>5</v>
       </c>
       <c r="B6" s="1">
-        <v>44865.828298611101</v>
+        <v>44865.8282986111</v>
       </c>
       <c r="C6" s="1">
-        <v>44865.828298611101</v>
+        <v>44865.8282986111</v>
       </c>
       <c r="E6" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="F6" t="s">
-        <v>181</v>
+        <v>213</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>173</v>
+        <v>205</v>
       </c>
       <c r="I6" t="s">
-        <v>182</v>
+        <v>214</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -5384,25 +6005,25 @@
         <v>6</v>
       </c>
       <c r="B7" s="1">
-        <v>44873.393229166701</v>
+        <v>44873.3932291667</v>
       </c>
       <c r="C7" s="1">
-        <v>44873.393229166701</v>
+        <v>44873.3932291667</v>
       </c>
       <c r="E7" t="s">
-        <v>183</v>
+        <v>215</v>
       </c>
       <c r="F7" t="s">
-        <v>184</v>
+        <v>216</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>185</v>
+        <v>217</v>
       </c>
       <c r="I7" t="s">
-        <v>186</v>
+        <v>218</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -5416,25 +6037,25 @@
         <v>7</v>
       </c>
       <c r="B8" s="1">
-        <v>44873.393449074101</v>
+        <v>44873.3934490741</v>
       </c>
       <c r="C8" s="1">
-        <v>44873.393449074101</v>
+        <v>44873.3934490741</v>
       </c>
       <c r="E8" t="s">
-        <v>183</v>
+        <v>215</v>
       </c>
       <c r="F8" t="s">
-        <v>187</v>
+        <v>219</v>
       </c>
       <c r="G8">
         <v>1</v>
       </c>
       <c r="H8" t="s">
-        <v>185</v>
+        <v>217</v>
       </c>
       <c r="I8" t="s">
-        <v>188</v>
+        <v>220</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -5448,25 +6069,25 @@
         <v>8</v>
       </c>
       <c r="B9" s="1">
-        <v>44882.803460648101</v>
+        <v>44882.8034606481</v>
       </c>
       <c r="C9" s="1">
-        <v>44882.803460648101</v>
+        <v>44882.8034606481</v>
       </c>
       <c r="E9" t="s">
-        <v>189</v>
+        <v>221</v>
       </c>
       <c r="F9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G9">
         <v>1</v>
       </c>
       <c r="H9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I9" t="s">
-        <v>190</v>
+        <v>222</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -5480,25 +6101,25 @@
         <v>9</v>
       </c>
       <c r="B10" s="1">
-        <v>44971.953680555598</v>
+        <v>44971.9536805556</v>
       </c>
       <c r="C10" s="1">
-        <v>44971.953680555598</v>
+        <v>44971.9536805556</v>
       </c>
       <c r="E10" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="F10" t="s">
-        <v>191</v>
+        <v>223</v>
       </c>
       <c r="G10">
         <v>0</v>
       </c>
       <c r="H10" t="s">
-        <v>173</v>
+        <v>205</v>
       </c>
       <c r="I10" t="s">
-        <v>192</v>
+        <v>224</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -5512,25 +6133,25 @@
         <v>10</v>
       </c>
       <c r="B11" s="1">
-        <v>44971.953680555598</v>
+        <v>44971.9536805556</v>
       </c>
       <c r="C11" s="1">
-        <v>44971.953680555598</v>
+        <v>44971.9536805556</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>349</v>
+        <v>60</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>193</v>
+        <v>225</v>
       </c>
       <c r="G11">
         <v>0</v>
       </c>
       <c r="H11" t="s">
-        <v>173</v>
+        <v>205</v>
       </c>
       <c r="I11" t="s">
-        <v>194</v>
+        <v>226</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -5540,21 +6161,22 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="120" orientation="portrait" horizontalDpi="203" verticalDpi="203" r:id="rId1"/>
+  <pageSetup paperSize="120" orientation="portrait" horizontalDpi="203" verticalDpi="203"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:K33"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="2" max="3" width="20.140625" customWidth="1"/>
     <col min="5" max="5" width="17.140625" customWidth="1"/>
-    <col min="6" max="6" width="23.85546875" customWidth="1"/>
-    <col min="7" max="7" width="67.85546875" customWidth="1"/>
+    <col min="6" max="6" width="23.859375" customWidth="1"/>
+    <col min="7" max="7" width="67.859375" customWidth="1"/>
     <col min="8" max="8" width="98" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5572,19 +6194,19 @@
         <v>20</v>
       </c>
       <c r="E1" t="s">
-        <v>195</v>
+        <v>227</v>
       </c>
       <c r="F1" t="s">
-        <v>196</v>
+        <v>228</v>
       </c>
       <c r="G1" t="s">
-        <v>197</v>
+        <v>229</v>
       </c>
       <c r="H1" t="s">
-        <v>137</v>
+        <v>160</v>
       </c>
       <c r="I1" t="s">
-        <v>198</v>
+        <v>230</v>
       </c>
       <c r="J1" t="s">
         <v>5</v>
@@ -5601,16 +6223,16 @@
         <v>44865.8664699074</v>
       </c>
       <c r="C2" s="1">
-        <v>44984.400081018503</v>
+        <v>44984.4000810185</v>
       </c>
       <c r="E2" t="s">
-        <v>199</v>
+        <v>231</v>
       </c>
       <c r="F2" t="s">
-        <v>200</v>
+        <v>232</v>
       </c>
       <c r="G2" t="s">
-        <v>201</v>
+        <v>233</v>
       </c>
       <c r="I2">
         <v>1</v>
@@ -5630,16 +6252,16 @@
         <v>44865.8664699074</v>
       </c>
       <c r="C3" s="1">
-        <v>44984.400081018503</v>
+        <v>44984.4000810185</v>
       </c>
       <c r="E3" t="s">
-        <v>202</v>
+        <v>234</v>
       </c>
       <c r="F3" t="s">
-        <v>203</v>
+        <v>235</v>
       </c>
       <c r="G3" t="s">
-        <v>204</v>
+        <v>236</v>
       </c>
       <c r="I3">
         <v>1</v>
@@ -5659,16 +6281,16 @@
         <v>44865.8664699074</v>
       </c>
       <c r="C4" s="1">
-        <v>44984.400081018503</v>
+        <v>44984.4000810185</v>
       </c>
       <c r="E4" t="s">
-        <v>205</v>
+        <v>237</v>
       </c>
       <c r="F4" t="s">
-        <v>206</v>
+        <v>238</v>
       </c>
       <c r="G4" t="s">
-        <v>207</v>
+        <v>239</v>
       </c>
       <c r="I4">
         <v>1</v>
@@ -5688,16 +6310,16 @@
         <v>44865.8664699074</v>
       </c>
       <c r="C5" s="1">
-        <v>44942.757025462997</v>
+        <v>44942.757025463</v>
       </c>
       <c r="E5" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="F5" t="s">
-        <v>209</v>
+        <v>241</v>
       </c>
       <c r="G5" t="s">
-        <v>210</v>
+        <v>242</v>
       </c>
       <c r="I5">
         <v>1</v>
@@ -5717,16 +6339,16 @@
         <v>44865.8664699074</v>
       </c>
       <c r="C6" s="1">
-        <v>44984.400081018503</v>
+        <v>44984.4000810185</v>
       </c>
       <c r="E6" t="s">
-        <v>211</v>
+        <v>243</v>
       </c>
       <c r="F6" t="s">
-        <v>212</v>
+        <v>244</v>
       </c>
       <c r="G6" t="s">
-        <v>213</v>
+        <v>245</v>
       </c>
       <c r="I6">
         <v>1</v>
@@ -5746,16 +6368,16 @@
         <v>44865.8664699074</v>
       </c>
       <c r="C7" s="1">
-        <v>44984.400081018503</v>
+        <v>44984.4000810185</v>
       </c>
       <c r="E7" t="s">
-        <v>214</v>
+        <v>246</v>
       </c>
       <c r="F7" t="s">
-        <v>215</v>
+        <v>247</v>
       </c>
       <c r="G7" t="s">
-        <v>216</v>
+        <v>248</v>
       </c>
       <c r="I7">
         <v>1</v>
@@ -5772,19 +6394,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="1">
-        <v>44865.868032407401</v>
+        <v>44865.8680324074</v>
       </c>
       <c r="C8" s="1">
-        <v>44887.691469907397</v>
+        <v>44887.6914699074</v>
       </c>
       <c r="E8" t="s">
-        <v>217</v>
+        <v>249</v>
       </c>
       <c r="F8" t="s">
-        <v>176</v>
+        <v>208</v>
       </c>
       <c r="H8" t="s">
-        <v>218</v>
+        <v>250</v>
       </c>
       <c r="I8">
         <v>2</v>
@@ -5801,19 +6423,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="1">
-        <v>44869.576631944401</v>
+        <v>44869.5766319444</v>
       </c>
       <c r="C9" s="1">
-        <v>44965.452013888898</v>
+        <v>44965.4520138889</v>
       </c>
       <c r="E9" t="s">
-        <v>219</v>
+        <v>251</v>
       </c>
       <c r="F9" t="s">
-        <v>180</v>
+        <v>212</v>
       </c>
       <c r="G9" t="s">
-        <v>220</v>
+        <v>252</v>
       </c>
       <c r="I9">
         <v>4</v>
@@ -5830,19 +6452,19 @@
         <v>9</v>
       </c>
       <c r="B10" s="1">
-        <v>44869.577037037001</v>
+        <v>44869.577037037</v>
       </c>
       <c r="C10" s="1">
-        <v>44869.679618055503</v>
+        <v>44869.6796180555</v>
       </c>
       <c r="E10" t="s">
-        <v>181</v>
+        <v>213</v>
       </c>
       <c r="F10" t="s">
-        <v>182</v>
+        <v>214</v>
       </c>
       <c r="G10" t="s">
-        <v>221</v>
+        <v>253</v>
       </c>
       <c r="I10">
         <v>5</v>
@@ -5859,16 +6481,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="1">
-        <v>44873.394305555601</v>
+        <v>44873.3943055556</v>
       </c>
       <c r="C11" s="1">
-        <v>44873.394305555601</v>
+        <v>44873.3943055556</v>
       </c>
       <c r="E11" t="s">
-        <v>222</v>
+        <v>254</v>
       </c>
       <c r="F11" t="s">
-        <v>223</v>
+        <v>255</v>
       </c>
       <c r="I11">
         <v>6</v>
@@ -5885,16 +6507,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="1">
-        <v>44873.394861111097</v>
+        <v>44873.3948611111</v>
       </c>
       <c r="C12" s="1">
-        <v>44873.394861111097</v>
+        <v>44873.3948611111</v>
       </c>
       <c r="E12" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="F12" t="s">
-        <v>225</v>
+        <v>257</v>
       </c>
       <c r="I12">
         <v>6</v>
@@ -5911,19 +6533,19 @@
         <v>12</v>
       </c>
       <c r="B13" s="1">
-        <v>44873.397835648102</v>
+        <v>44873.3978356481</v>
       </c>
       <c r="C13" s="1">
-        <v>44873.397835648102</v>
+        <v>44873.3978356481</v>
       </c>
       <c r="E13" t="s">
-        <v>226</v>
+        <v>258</v>
       </c>
       <c r="F13" t="s">
-        <v>227</v>
+        <v>259</v>
       </c>
       <c r="H13" t="s">
-        <v>228</v>
+        <v>260</v>
       </c>
       <c r="I13">
         <v>6</v>
@@ -5940,19 +6562,19 @@
         <v>13</v>
       </c>
       <c r="B14" s="1">
-        <v>44873.404872685198</v>
+        <v>44873.4048726852</v>
       </c>
       <c r="C14" s="1">
-        <v>44873.404872685198</v>
+        <v>44873.4048726852</v>
       </c>
       <c r="E14" t="s">
-        <v>229</v>
+        <v>261</v>
       </c>
       <c r="F14" t="s">
-        <v>230</v>
+        <v>262</v>
       </c>
       <c r="H14" t="s">
-        <v>231</v>
+        <v>263</v>
       </c>
       <c r="I14">
         <v>6</v>
@@ -5969,19 +6591,19 @@
         <v>14</v>
       </c>
       <c r="B15" s="1">
-        <v>44873.948194444398</v>
+        <v>44873.9481944444</v>
       </c>
       <c r="C15" s="1">
-        <v>44873.948194444398</v>
+        <v>44873.9481944444</v>
       </c>
       <c r="E15" t="s">
-        <v>232</v>
+        <v>264</v>
       </c>
       <c r="F15" t="s">
-        <v>233</v>
+        <v>265</v>
       </c>
       <c r="G15" t="s">
-        <v>234</v>
+        <v>266</v>
       </c>
       <c r="I15">
         <v>6</v>
@@ -5998,19 +6620,19 @@
         <v>15</v>
       </c>
       <c r="B16" s="1">
-        <v>44873.948611111096</v>
+        <v>44873.9486111111</v>
       </c>
       <c r="C16" s="1">
-        <v>44873.948611111096</v>
+        <v>44873.9486111111</v>
       </c>
       <c r="E16" t="s">
-        <v>235</v>
+        <v>267</v>
       </c>
       <c r="F16" t="s">
-        <v>236</v>
+        <v>268</v>
       </c>
       <c r="G16" t="s">
-        <v>237</v>
+        <v>269</v>
       </c>
       <c r="I16">
         <v>6</v>
@@ -6027,19 +6649,19 @@
         <v>16</v>
       </c>
       <c r="B17" s="1">
-        <v>44880.940173611103</v>
+        <v>44880.9401736111</v>
       </c>
       <c r="C17" s="1">
-        <v>44880.940173611103</v>
+        <v>44880.9401736111</v>
       </c>
       <c r="E17" t="s">
-        <v>238</v>
+        <v>270</v>
       </c>
       <c r="F17" t="s">
-        <v>239</v>
+        <v>271</v>
       </c>
       <c r="H17" t="s">
-        <v>240</v>
+        <v>272</v>
       </c>
       <c r="I17">
         <v>6</v>
@@ -6056,19 +6678,19 @@
         <v>17</v>
       </c>
       <c r="B18" s="1">
-        <v>44880.941412036998</v>
+        <v>44880.941412037</v>
       </c>
       <c r="C18" s="1">
-        <v>44880.941412036998</v>
+        <v>44880.941412037</v>
       </c>
       <c r="E18" t="s">
-        <v>241</v>
+        <v>273</v>
       </c>
       <c r="F18" t="s">
-        <v>242</v>
+        <v>274</v>
       </c>
       <c r="H18" t="s">
-        <v>243</v>
+        <v>275</v>
       </c>
       <c r="I18">
         <v>6</v>
@@ -6091,13 +6713,13 @@
         <v>44882.8044212963</v>
       </c>
       <c r="E19" t="s">
-        <v>244</v>
+        <v>276</v>
       </c>
       <c r="F19" t="s">
-        <v>245</v>
+        <v>277</v>
       </c>
       <c r="H19" t="s">
-        <v>246</v>
+        <v>278</v>
       </c>
       <c r="I19">
         <v>8</v>
@@ -6114,22 +6736,22 @@
         <v>19</v>
       </c>
       <c r="B20" s="1">
-        <v>44882.805381944403</v>
+        <v>44882.8053819444</v>
       </c>
       <c r="C20" s="1">
-        <v>44882.805381944403</v>
+        <v>44882.8053819444</v>
       </c>
       <c r="E20" t="s">
-        <v>247</v>
+        <v>279</v>
       </c>
       <c r="F20" t="s">
-        <v>248</v>
+        <v>280</v>
       </c>
       <c r="G20" t="s">
-        <v>249</v>
+        <v>281</v>
       </c>
       <c r="H20" t="s">
-        <v>250</v>
+        <v>282</v>
       </c>
       <c r="I20">
         <v>8</v>
@@ -6146,22 +6768,22 @@
         <v>20</v>
       </c>
       <c r="B21" s="1">
-        <v>44882.805740740703</v>
+        <v>44882.8057407407</v>
       </c>
       <c r="C21" s="1">
-        <v>44882.805740740703</v>
+        <v>44882.8057407407</v>
       </c>
       <c r="E21" t="s">
-        <v>251</v>
+        <v>283</v>
       </c>
       <c r="F21" t="s">
-        <v>252</v>
+        <v>284</v>
       </c>
       <c r="G21" t="s">
-        <v>253</v>
+        <v>285</v>
       </c>
       <c r="H21" t="s">
-        <v>254</v>
+        <v>286</v>
       </c>
       <c r="I21">
         <v>8</v>
@@ -6178,22 +6800,22 @@
         <v>21</v>
       </c>
       <c r="B22" s="1">
-        <v>44882.814594907402</v>
+        <v>44882.8145949074</v>
       </c>
       <c r="C22" s="1">
-        <v>44882.814594907402</v>
+        <v>44882.8145949074</v>
       </c>
       <c r="E22" t="s">
-        <v>255</v>
+        <v>287</v>
       </c>
       <c r="F22" t="s">
-        <v>256</v>
+        <v>288</v>
       </c>
       <c r="G22" t="s">
-        <v>257</v>
+        <v>289</v>
       </c>
       <c r="H22" t="s">
-        <v>258</v>
+        <v>290</v>
       </c>
       <c r="I22">
         <v>8</v>
@@ -6210,22 +6832,22 @@
         <v>22</v>
       </c>
       <c r="B23" s="1">
-        <v>44882.815324074101</v>
+        <v>44882.8153240741</v>
       </c>
       <c r="C23" s="1">
-        <v>44882.815324074101</v>
+        <v>44882.8153240741</v>
       </c>
       <c r="E23" t="s">
-        <v>259</v>
+        <v>291</v>
       </c>
       <c r="F23" t="s">
-        <v>260</v>
+        <v>292</v>
       </c>
       <c r="G23" t="s">
-        <v>261</v>
+        <v>293</v>
       </c>
       <c r="H23" t="s">
-        <v>262</v>
+        <v>294</v>
       </c>
       <c r="I23">
         <v>8</v>
@@ -6242,22 +6864,22 @@
         <v>23</v>
       </c>
       <c r="B24" s="1">
-        <v>44882.816689814797</v>
+        <v>44882.8166898148</v>
       </c>
       <c r="C24" s="1">
-        <v>44882.816689814797</v>
+        <v>44882.8166898148</v>
       </c>
       <c r="E24" t="s">
-        <v>263</v>
+        <v>295</v>
       </c>
       <c r="F24" t="s">
-        <v>264</v>
+        <v>296</v>
       </c>
       <c r="G24" t="s">
-        <v>265</v>
+        <v>297</v>
       </c>
       <c r="H24" t="s">
-        <v>266</v>
+        <v>298</v>
       </c>
       <c r="I24">
         <v>8</v>
@@ -6274,19 +6896,19 @@
         <v>25</v>
       </c>
       <c r="B25" s="1">
-        <v>44971.954965277801</v>
+        <v>44971.9549652778</v>
       </c>
       <c r="C25" s="1">
-        <v>44984.409745370402</v>
+        <v>44984.4097453704</v>
       </c>
       <c r="E25" t="s">
-        <v>267</v>
+        <v>299</v>
       </c>
       <c r="F25" t="s">
-        <v>268</v>
+        <v>300</v>
       </c>
       <c r="G25" t="s">
-        <v>269</v>
+        <v>301</v>
       </c>
       <c r="I25">
         <v>9</v>
@@ -6303,16 +6925,16 @@
         <v>26</v>
       </c>
       <c r="B26" s="1">
-        <v>44971.955520833297</v>
+        <v>44971.9555208333</v>
       </c>
       <c r="C26" s="1">
-        <v>44984.409745370402</v>
+        <v>44984.4097453704</v>
       </c>
       <c r="E26" t="s">
-        <v>270</v>
+        <v>302</v>
       </c>
       <c r="F26" t="s">
-        <v>271</v>
+        <v>303</v>
       </c>
       <c r="I26">
         <v>9</v>
@@ -6329,19 +6951,19 @@
         <v>27</v>
       </c>
       <c r="B27" s="1">
-        <v>44971.956076388902</v>
+        <v>44971.9560763889</v>
       </c>
       <c r="C27" s="1">
-        <v>44984.409745370402</v>
+        <v>44984.4097453704</v>
       </c>
       <c r="E27" t="s">
-        <v>272</v>
+        <v>304</v>
       </c>
       <c r="F27" t="s">
-        <v>273</v>
+        <v>305</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>274</v>
+        <v>306</v>
       </c>
       <c r="I27">
         <v>9</v>
@@ -6358,16 +6980,16 @@
         <v>28</v>
       </c>
       <c r="B28" s="1">
-        <v>44983.917581018497</v>
+        <v>44983.9175810185</v>
       </c>
       <c r="C28" s="1">
-        <v>44984.409745370402</v>
+        <v>44984.4097453704</v>
       </c>
       <c r="E28" t="s">
-        <v>275</v>
+        <v>307</v>
       </c>
       <c r="F28" t="s">
-        <v>276</v>
+        <v>308</v>
       </c>
       <c r="I28">
         <v>9</v>
@@ -6384,16 +7006,16 @@
         <v>29</v>
       </c>
       <c r="B29" s="1">
-        <v>44983.917893518497</v>
+        <v>44983.9178935185</v>
       </c>
       <c r="C29" s="1">
-        <v>44984.409745370402</v>
+        <v>44984.4097453704</v>
       </c>
       <c r="E29" t="s">
-        <v>277</v>
+        <v>309</v>
       </c>
       <c r="F29" t="s">
-        <v>278</v>
+        <v>310</v>
       </c>
       <c r="I29">
         <v>9</v>
@@ -6410,16 +7032,16 @@
         <v>34</v>
       </c>
       <c r="B30" s="1">
-        <v>44983.917893518497</v>
+        <v>44983.9178935185</v>
       </c>
       <c r="C30" s="1">
-        <v>44984.409745370402</v>
+        <v>44984.4097453704</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>279</v>
+        <v>311</v>
       </c>
       <c r="F30" t="s">
-        <v>280</v>
+        <v>312</v>
       </c>
       <c r="G30" s="4"/>
       <c r="I30">
@@ -6437,16 +7059,16 @@
         <v>35</v>
       </c>
       <c r="B31" s="1">
-        <v>44983.917893518497</v>
+        <v>44983.9178935185</v>
       </c>
       <c r="C31" s="1">
-        <v>44984.409745370402</v>
+        <v>44984.4097453704</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>281</v>
+        <v>313</v>
       </c>
       <c r="F31" t="s">
-        <v>282</v>
+        <v>314</v>
       </c>
       <c r="G31" s="5"/>
       <c r="I31">
@@ -6464,19 +7086,19 @@
         <v>36</v>
       </c>
       <c r="B32" s="1">
-        <v>44983.917893518497</v>
+        <v>44983.9178935185</v>
       </c>
       <c r="C32" s="1">
-        <v>44984.409745370402</v>
+        <v>44984.4097453704</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>283</v>
+        <v>315</v>
       </c>
       <c r="F32" t="s">
-        <v>284</v>
+        <v>316</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>285</v>
+        <v>317</v>
       </c>
       <c r="I32">
         <v>10</v>
@@ -6493,16 +7115,16 @@
         <v>37</v>
       </c>
       <c r="B33" s="1">
-        <v>44983.917893518497</v>
+        <v>44983.9178935185</v>
       </c>
       <c r="C33" s="1">
-        <v>44984.409745370402</v>
+        <v>44984.4097453704</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>286</v>
+        <v>318</v>
       </c>
       <c r="F33" t="s">
-        <v>287</v>
+        <v>319</v>
       </c>
       <c r="G33" s="5">
         <v>25</v>
@@ -6518,26 +7140,27 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="G27" r:id="rId1" xr:uid="{00000000-0004-0000-0700-000000000000}"/>
+    <hyperlink ref="G27" r:id="rId1" display="https://kinit.ktianc.top"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:I3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="2"/>
   <cols>
-    <col min="2" max="3" width="18.85546875" customWidth="1"/>
-    <col min="4" max="4" width="17.42578125" customWidth="1"/>
-    <col min="5" max="5" width="9.85546875" customWidth="1"/>
+    <col min="2" max="3" width="18.859375" customWidth="1"/>
+    <col min="4" max="4" width="17.4296875" customWidth="1"/>
+    <col min="5" max="5" width="9.859375" customWidth="1"/>
     <col min="6" max="6" width="11.140625" customWidth="1"/>
-    <col min="7" max="7" width="9.28515625" customWidth="1"/>
-    <col min="9" max="9" width="15.28515625" customWidth="1"/>
+    <col min="7" max="7" width="9.2890625" customWidth="1"/>
+    <col min="9" max="9" width="15.2890625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -6557,16 +7180,16 @@
         <v>21</v>
       </c>
       <c r="F1" t="s">
-        <v>113</v>
+        <v>133</v>
       </c>
       <c r="G1" t="s">
-        <v>288</v>
+        <v>320</v>
       </c>
       <c r="H1" t="s">
-        <v>124</v>
+        <v>146</v>
       </c>
       <c r="I1" t="s">
-        <v>289</v>
+        <v>321</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -6574,16 +7197,16 @@
         <v>3</v>
       </c>
       <c r="B2" s="1">
-        <v>44984.656585648103</v>
+        <v>44984.6565856481</v>
       </c>
       <c r="C2" s="1">
-        <v>44984.656585648103</v>
+        <v>44984.6565856481</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>290</v>
+        <v>322</v>
       </c>
       <c r="G2" t="s">
         <v>38</v>
@@ -6609,7 +7232,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="s">
-        <v>291</v>
+        <v>323</v>
       </c>
       <c r="G3" t="s">
         <v>38</v>
@@ -6622,7 +7245,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/kinit-api/scripts/initialize/data/init.xlsx
+++ b/kinit-api/scripts/initialize/data/init.xlsx
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="497" uniqueCount="348">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="496" uniqueCount="346">
   <si>
     <t>title</t>
   </si>
@@ -497,12 +497,6 @@
   </si>
   <si>
     <t>is_wx_server_openid</t>
-  </si>
-  <si>
-    <t>kinit</t>
-  </si>
-  <si>
-    <t>$2b$12$Ce7eSUKIIl8DMKeDyNHyr.Dp4aesQCM70RePigRVEny1Eql31R0Cq</t>
   </si>
   <si>
     <t>127.0.0.1</t>
@@ -1126,7 +1120,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="yyyy/m/d\ h:mm:ss"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -1147,7 +1141,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <name val="宋体"/>
+      <name val="宋体-简"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1292,11 +1286,6 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="33">
@@ -4385,22 +4374,22 @@
         <v>21</v>
       </c>
       <c r="F1" t="s">
+        <v>322</v>
+      </c>
+      <c r="G1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I1" t="s">
         <v>324</v>
-      </c>
-      <c r="G1" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" t="s">
-        <v>325</v>
-      </c>
-      <c r="I1" t="s">
-        <v>326</v>
       </c>
       <c r="J1" t="s">
         <v>146</v>
       </c>
       <c r="K1" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -4420,10 +4409,10 @@
         <v>3</v>
       </c>
       <c r="G2" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="H2" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -4452,10 +4441,10 @@
         <v>3</v>
       </c>
       <c r="G3" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="H3" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4484,10 +4473,10 @@
         <v>3</v>
       </c>
       <c r="G4" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="H4" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4516,10 +4505,10 @@
         <v>3</v>
       </c>
       <c r="G5" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="H5" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4548,10 +4537,10 @@
         <v>4</v>
       </c>
       <c r="G6" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="H6" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4580,10 +4569,10 @@
         <v>4</v>
       </c>
       <c r="G7" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="H7" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4612,10 +4601,10 @@
         <v>4</v>
       </c>
       <c r="G8" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="H8" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -4650,7 +4639,7 @@
         <v>133</v>
       </c>
       <c r="B1" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C1" t="s">
         <v>5</v>
@@ -4662,10 +4651,10 @@
         <v>135</v>
       </c>
       <c r="F1" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="G1" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="H1" t="s">
         <v>142</v>
@@ -4691,10 +4680,10 @@
     </row>
     <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B2" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -4729,10 +4718,10 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -4839,6 +4828,7 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="1"/>
   <cols>
     <col min="2" max="2" width="25.6484375" customWidth="1"/>
+    <col min="6" max="6" width="32.6796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19">
@@ -4902,16 +4892,16 @@
     </row>
     <row r="2" spans="1:19">
       <c r="B2">
-        <v>17302869369</v>
-      </c>
-      <c r="D2" t="s">
-        <v>153</v>
+        <v>13888888888</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>138</v>
       </c>
       <c r="E2" t="s">
         <v>139</v>
       </c>
-      <c r="F2" t="s">
-        <v>154</v>
+      <c r="F2">
+        <v>123456</v>
       </c>
       <c r="G2" t="s">
         <v>38</v>
@@ -4923,11 +4913,9 @@
         <v>1</v>
       </c>
       <c r="J2" t="s">
-        <v>155</v>
-      </c>
-      <c r="K2" s="1">
-        <v>45311.4639583333</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="K2" s="1"/>
       <c r="L2">
         <v>1</v>
       </c>
@@ -4937,12 +4925,8 @@
       <c r="O2">
         <v>1</v>
       </c>
-      <c r="P2" s="1">
-        <v>44784.8451851852</v>
-      </c>
-      <c r="Q2" s="1">
-        <v>45311.4639236111</v>
-      </c>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1"/>
       <c r="S2">
         <v>0</v>
       </c>
@@ -4961,10 +4945,10 @@
   <sheetData>
     <row r="1" ht="17" spans="1:2">
       <c r="A1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -4990,16 +4974,16 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C1" t="s">
         <v>5</v>
       </c>
       <c r="D1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E1" t="s">
         <v>17</v>
@@ -5019,10 +5003,10 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -5042,10 +5026,10 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -5065,10 +5049,10 @@
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B4" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -5088,10 +5072,10 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B5" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -5111,16 +5095,16 @@
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
+        <v>167</v>
+      </c>
+      <c r="B6" t="s">
+        <v>168</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6" t="s">
         <v>169</v>
-      </c>
-      <c r="B6" t="s">
-        <v>170</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6" t="s">
-        <v>171</v>
       </c>
       <c r="E6">
         <v>5</v>
@@ -5137,10 +5121,10 @@
     </row>
     <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B7" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -5172,25 +5156,25 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C1" t="s">
         <v>5</v>
       </c>
       <c r="D1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E1" t="s">
         <v>7</v>
       </c>
       <c r="F1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="G1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="H1" t="s">
         <v>17</v>
@@ -5210,7 +5194,7 @@
     </row>
     <row r="2" spans="1:12">
       <c r="A2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B2" t="s">
         <v>27</v>
@@ -5242,7 +5226,7 @@
     </row>
     <row r="3" spans="1:12">
       <c r="A3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B3" t="s">
         <v>38</v>
@@ -5274,7 +5258,7 @@
     </row>
     <row r="4" spans="1:12">
       <c r="A4" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B4" t="s">
         <v>27</v>
@@ -5306,7 +5290,7 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B5" t="s">
         <v>38</v>
@@ -5338,7 +5322,7 @@
     </row>
     <row r="6" spans="1:12">
       <c r="A6" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B6" t="s">
         <v>70</v>
@@ -5370,7 +5354,7 @@
     </row>
     <row r="7" spans="1:12">
       <c r="A7" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B7" t="s">
         <v>27</v>
@@ -5402,7 +5386,7 @@
     </row>
     <row r="8" spans="1:12">
       <c r="A8" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B8" t="s">
         <v>38</v>
@@ -5434,7 +5418,7 @@
     </row>
     <row r="9" spans="1:12">
       <c r="A9" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B9" t="s">
         <v>27</v>
@@ -5466,7 +5450,7 @@
     </row>
     <row r="10" spans="1:12">
       <c r="A10" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B10" t="s">
         <v>38</v>
@@ -5498,7 +5482,7 @@
     </row>
     <row r="11" spans="1:12">
       <c r="A11" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B11" t="s">
         <v>70</v>
@@ -5530,10 +5514,10 @@
     </row>
     <row r="12" spans="1:12">
       <c r="A12" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B12" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -5562,10 +5546,10 @@
     </row>
     <row r="13" spans="1:12">
       <c r="A13" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B13" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -5594,10 +5578,10 @@
     </row>
     <row r="14" spans="1:12">
       <c r="A14" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B14" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -5626,7 +5610,7 @@
     </row>
     <row r="15" spans="1:12">
       <c r="A15" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B15" t="s">
         <v>27</v>
@@ -5658,7 +5642,7 @@
     </row>
     <row r="16" spans="1:12">
       <c r="A16" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B16" t="s">
         <v>38</v>
@@ -5690,7 +5674,7 @@
     </row>
     <row r="17" spans="1:12">
       <c r="A17" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B17" t="s">
         <v>70</v>
@@ -5722,10 +5706,10 @@
     </row>
     <row r="18" spans="1:12">
       <c r="A18" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B18" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -5754,10 +5738,10 @@
     </row>
     <row r="19" spans="1:12">
       <c r="A19" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B19" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -5822,16 +5806,16 @@
         <v>0</v>
       </c>
       <c r="F1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="G1" t="s">
         <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="I1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="J1" t="s">
         <v>5</v>
@@ -5854,16 +5838,16 @@
         <v>60</v>
       </c>
       <c r="F2" t="s">
+        <v>202</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2" t="s">
+        <v>203</v>
+      </c>
+      <c r="I2" t="s">
         <v>204</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2" t="s">
-        <v>205</v>
-      </c>
-      <c r="I2" t="s">
-        <v>206</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -5886,16 +5870,16 @@
         <v>60</v>
       </c>
       <c r="F3" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G3">
         <v>1</v>
       </c>
       <c r="H3" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="I3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="J3">
         <v>1</v>
@@ -5918,16 +5902,16 @@
         <v>60</v>
       </c>
       <c r="F4" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="G4">
         <v>1</v>
       </c>
       <c r="H4" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="I4" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -5950,16 +5934,16 @@
         <v>60</v>
       </c>
       <c r="F5" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="I5" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -5982,16 +5966,16 @@
         <v>60</v>
       </c>
       <c r="F6" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="I6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -6011,19 +5995,19 @@
         <v>44873.3932291667</v>
       </c>
       <c r="E7" t="s">
+        <v>213</v>
+      </c>
+      <c r="F7" t="s">
+        <v>214</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7" t="s">
         <v>215</v>
       </c>
-      <c r="F7" t="s">
+      <c r="I7" t="s">
         <v>216</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7" t="s">
-        <v>217</v>
-      </c>
-      <c r="I7" t="s">
-        <v>218</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -6043,19 +6027,19 @@
         <v>44873.3934490741</v>
       </c>
       <c r="E8" t="s">
+        <v>213</v>
+      </c>
+      <c r="F8" t="s">
+        <v>217</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8" t="s">
         <v>215</v>
       </c>
-      <c r="F8" t="s">
-        <v>219</v>
-      </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
-      <c r="H8" t="s">
-        <v>217</v>
-      </c>
       <c r="I8" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -6075,7 +6059,7 @@
         <v>44882.8034606481</v>
       </c>
       <c r="E9" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="F9" t="s">
         <v>42</v>
@@ -6087,7 +6071,7 @@
         <v>44</v>
       </c>
       <c r="I9" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -6110,16 +6094,16 @@
         <v>60</v>
       </c>
       <c r="F10" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="G10">
         <v>0</v>
       </c>
       <c r="H10" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="I10" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -6138,20 +6122,20 @@
       <c r="C11" s="1">
         <v>44971.9536805556</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="E11" s="3" t="s">
         <v>60</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="G11">
         <v>0</v>
       </c>
       <c r="H11" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="I11" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -6194,19 +6178,19 @@
         <v>20</v>
       </c>
       <c r="E1" t="s">
+        <v>225</v>
+      </c>
+      <c r="F1" t="s">
+        <v>226</v>
+      </c>
+      <c r="G1" t="s">
         <v>227</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
+        <v>158</v>
+      </c>
+      <c r="I1" t="s">
         <v>228</v>
-      </c>
-      <c r="G1" t="s">
-        <v>229</v>
-      </c>
-      <c r="H1" t="s">
-        <v>160</v>
-      </c>
-      <c r="I1" t="s">
-        <v>230</v>
       </c>
       <c r="J1" t="s">
         <v>5</v>
@@ -6226,13 +6210,13 @@
         <v>44984.4000810185</v>
       </c>
       <c r="E2" t="s">
+        <v>229</v>
+      </c>
+      <c r="F2" t="s">
+        <v>230</v>
+      </c>
+      <c r="G2" t="s">
         <v>231</v>
-      </c>
-      <c r="F2" t="s">
-        <v>232</v>
-      </c>
-      <c r="G2" t="s">
-        <v>233</v>
       </c>
       <c r="I2">
         <v>1</v>
@@ -6255,13 +6239,13 @@
         <v>44984.4000810185</v>
       </c>
       <c r="E3" t="s">
+        <v>232</v>
+      </c>
+      <c r="F3" t="s">
+        <v>233</v>
+      </c>
+      <c r="G3" t="s">
         <v>234</v>
-      </c>
-      <c r="F3" t="s">
-        <v>235</v>
-      </c>
-      <c r="G3" t="s">
-        <v>236</v>
       </c>
       <c r="I3">
         <v>1</v>
@@ -6284,13 +6268,13 @@
         <v>44984.4000810185</v>
       </c>
       <c r="E4" t="s">
+        <v>235</v>
+      </c>
+      <c r="F4" t="s">
+        <v>236</v>
+      </c>
+      <c r="G4" t="s">
         <v>237</v>
-      </c>
-      <c r="F4" t="s">
-        <v>238</v>
-      </c>
-      <c r="G4" t="s">
-        <v>239</v>
       </c>
       <c r="I4">
         <v>1</v>
@@ -6313,13 +6297,13 @@
         <v>44942.757025463</v>
       </c>
       <c r="E5" t="s">
+        <v>238</v>
+      </c>
+      <c r="F5" t="s">
+        <v>239</v>
+      </c>
+      <c r="G5" t="s">
         <v>240</v>
-      </c>
-      <c r="F5" t="s">
-        <v>241</v>
-      </c>
-      <c r="G5" t="s">
-        <v>242</v>
       </c>
       <c r="I5">
         <v>1</v>
@@ -6342,13 +6326,13 @@
         <v>44984.4000810185</v>
       </c>
       <c r="E6" t="s">
+        <v>241</v>
+      </c>
+      <c r="F6" t="s">
+        <v>242</v>
+      </c>
+      <c r="G6" t="s">
         <v>243</v>
-      </c>
-      <c r="F6" t="s">
-        <v>244</v>
-      </c>
-      <c r="G6" t="s">
-        <v>245</v>
       </c>
       <c r="I6">
         <v>1</v>
@@ -6371,13 +6355,13 @@
         <v>44984.4000810185</v>
       </c>
       <c r="E7" t="s">
+        <v>244</v>
+      </c>
+      <c r="F7" t="s">
+        <v>245</v>
+      </c>
+      <c r="G7" t="s">
         <v>246</v>
-      </c>
-      <c r="F7" t="s">
-        <v>247</v>
-      </c>
-      <c r="G7" t="s">
-        <v>248</v>
       </c>
       <c r="I7">
         <v>1</v>
@@ -6400,13 +6384,13 @@
         <v>44887.6914699074</v>
       </c>
       <c r="E8" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="F8" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="H8" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="I8">
         <v>2</v>
@@ -6429,13 +6413,13 @@
         <v>44965.4520138889</v>
       </c>
       <c r="E9" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="F9" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="G9" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="I9">
         <v>4</v>
@@ -6458,13 +6442,13 @@
         <v>44869.6796180555</v>
       </c>
       <c r="E10" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="F10" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="G10" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="I10">
         <v>5</v>
@@ -6487,10 +6471,10 @@
         <v>44873.3943055556</v>
       </c>
       <c r="E11" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="F11" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="I11">
         <v>6</v>
@@ -6513,10 +6497,10 @@
         <v>44873.3948611111</v>
       </c>
       <c r="E12" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="F12" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="I12">
         <v>6</v>
@@ -6539,13 +6523,13 @@
         <v>44873.3978356481</v>
       </c>
       <c r="E13" t="s">
+        <v>256</v>
+      </c>
+      <c r="F13" t="s">
+        <v>257</v>
+      </c>
+      <c r="H13" t="s">
         <v>258</v>
-      </c>
-      <c r="F13" t="s">
-        <v>259</v>
-      </c>
-      <c r="H13" t="s">
-        <v>260</v>
       </c>
       <c r="I13">
         <v>6</v>
@@ -6568,13 +6552,13 @@
         <v>44873.4048726852</v>
       </c>
       <c r="E14" t="s">
+        <v>259</v>
+      </c>
+      <c r="F14" t="s">
+        <v>260</v>
+      </c>
+      <c r="H14" t="s">
         <v>261</v>
-      </c>
-      <c r="F14" t="s">
-        <v>262</v>
-      </c>
-      <c r="H14" t="s">
-        <v>263</v>
       </c>
       <c r="I14">
         <v>6</v>
@@ -6597,13 +6581,13 @@
         <v>44873.9481944444</v>
       </c>
       <c r="E15" t="s">
+        <v>262</v>
+      </c>
+      <c r="F15" t="s">
+        <v>263</v>
+      </c>
+      <c r="G15" t="s">
         <v>264</v>
-      </c>
-      <c r="F15" t="s">
-        <v>265</v>
-      </c>
-      <c r="G15" t="s">
-        <v>266</v>
       </c>
       <c r="I15">
         <v>6</v>
@@ -6626,13 +6610,13 @@
         <v>44873.9486111111</v>
       </c>
       <c r="E16" t="s">
+        <v>265</v>
+      </c>
+      <c r="F16" t="s">
+        <v>266</v>
+      </c>
+      <c r="G16" t="s">
         <v>267</v>
-      </c>
-      <c r="F16" t="s">
-        <v>268</v>
-      </c>
-      <c r="G16" t="s">
-        <v>269</v>
       </c>
       <c r="I16">
         <v>6</v>
@@ -6655,13 +6639,13 @@
         <v>44880.9401736111</v>
       </c>
       <c r="E17" t="s">
+        <v>268</v>
+      </c>
+      <c r="F17" t="s">
+        <v>269</v>
+      </c>
+      <c r="H17" t="s">
         <v>270</v>
-      </c>
-      <c r="F17" t="s">
-        <v>271</v>
-      </c>
-      <c r="H17" t="s">
-        <v>272</v>
       </c>
       <c r="I17">
         <v>6</v>
@@ -6684,13 +6668,13 @@
         <v>44880.941412037</v>
       </c>
       <c r="E18" t="s">
+        <v>271</v>
+      </c>
+      <c r="F18" t="s">
+        <v>272</v>
+      </c>
+      <c r="H18" t="s">
         <v>273</v>
-      </c>
-      <c r="F18" t="s">
-        <v>274</v>
-      </c>
-      <c r="H18" t="s">
-        <v>275</v>
       </c>
       <c r="I18">
         <v>6</v>
@@ -6713,13 +6697,13 @@
         <v>44882.8044212963</v>
       </c>
       <c r="E19" t="s">
+        <v>274</v>
+      </c>
+      <c r="F19" t="s">
+        <v>275</v>
+      </c>
+      <c r="H19" t="s">
         <v>276</v>
-      </c>
-      <c r="F19" t="s">
-        <v>277</v>
-      </c>
-      <c r="H19" t="s">
-        <v>278</v>
       </c>
       <c r="I19">
         <v>8</v>
@@ -6742,16 +6726,16 @@
         <v>44882.8053819444</v>
       </c>
       <c r="E20" t="s">
+        <v>277</v>
+      </c>
+      <c r="F20" t="s">
+        <v>278</v>
+      </c>
+      <c r="G20" t="s">
         <v>279</v>
       </c>
-      <c r="F20" t="s">
+      <c r="H20" t="s">
         <v>280</v>
-      </c>
-      <c r="G20" t="s">
-        <v>281</v>
-      </c>
-      <c r="H20" t="s">
-        <v>282</v>
       </c>
       <c r="I20">
         <v>8</v>
@@ -6774,16 +6758,16 @@
         <v>44882.8057407407</v>
       </c>
       <c r="E21" t="s">
+        <v>281</v>
+      </c>
+      <c r="F21" t="s">
+        <v>282</v>
+      </c>
+      <c r="G21" t="s">
         <v>283</v>
       </c>
-      <c r="F21" t="s">
+      <c r="H21" t="s">
         <v>284</v>
-      </c>
-      <c r="G21" t="s">
-        <v>285</v>
-      </c>
-      <c r="H21" t="s">
-        <v>286</v>
       </c>
       <c r="I21">
         <v>8</v>
@@ -6806,16 +6790,16 @@
         <v>44882.8145949074</v>
       </c>
       <c r="E22" t="s">
+        <v>285</v>
+      </c>
+      <c r="F22" t="s">
+        <v>286</v>
+      </c>
+      <c r="G22" t="s">
         <v>287</v>
       </c>
-      <c r="F22" t="s">
+      <c r="H22" t="s">
         <v>288</v>
-      </c>
-      <c r="G22" t="s">
-        <v>289</v>
-      </c>
-      <c r="H22" t="s">
-        <v>290</v>
       </c>
       <c r="I22">
         <v>8</v>
@@ -6838,16 +6822,16 @@
         <v>44882.8153240741</v>
       </c>
       <c r="E23" t="s">
+        <v>289</v>
+      </c>
+      <c r="F23" t="s">
+        <v>290</v>
+      </c>
+      <c r="G23" t="s">
         <v>291</v>
       </c>
-      <c r="F23" t="s">
+      <c r="H23" t="s">
         <v>292</v>
-      </c>
-      <c r="G23" t="s">
-        <v>293</v>
-      </c>
-      <c r="H23" t="s">
-        <v>294</v>
       </c>
       <c r="I23">
         <v>8</v>
@@ -6870,16 +6854,16 @@
         <v>44882.8166898148</v>
       </c>
       <c r="E24" t="s">
+        <v>293</v>
+      </c>
+      <c r="F24" t="s">
+        <v>294</v>
+      </c>
+      <c r="G24" t="s">
         <v>295</v>
       </c>
-      <c r="F24" t="s">
+      <c r="H24" t="s">
         <v>296</v>
-      </c>
-      <c r="G24" t="s">
-        <v>297</v>
-      </c>
-      <c r="H24" t="s">
-        <v>298</v>
       </c>
       <c r="I24">
         <v>8</v>
@@ -6902,13 +6886,13 @@
         <v>44984.4097453704</v>
       </c>
       <c r="E25" t="s">
+        <v>297</v>
+      </c>
+      <c r="F25" t="s">
+        <v>298</v>
+      </c>
+      <c r="G25" t="s">
         <v>299</v>
-      </c>
-      <c r="F25" t="s">
-        <v>300</v>
-      </c>
-      <c r="G25" t="s">
-        <v>301</v>
       </c>
       <c r="I25">
         <v>9</v>
@@ -6931,10 +6915,10 @@
         <v>44984.4097453704</v>
       </c>
       <c r="E26" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="F26" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="I26">
         <v>9</v>
@@ -6957,13 +6941,13 @@
         <v>44984.4097453704</v>
       </c>
       <c r="E27" t="s">
+        <v>302</v>
+      </c>
+      <c r="F27" t="s">
+        <v>303</v>
+      </c>
+      <c r="G27" s="2" t="s">
         <v>304</v>
-      </c>
-      <c r="F27" t="s">
-        <v>305</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>306</v>
       </c>
       <c r="I27">
         <v>9</v>
@@ -6986,10 +6970,10 @@
         <v>44984.4097453704</v>
       </c>
       <c r="E28" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F28" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="I28">
         <v>9</v>
@@ -7012,10 +6996,10 @@
         <v>44984.4097453704</v>
       </c>
       <c r="E29" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F29" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="I29">
         <v>9</v>
@@ -7038,10 +7022,10 @@
         <v>44984.4097453704</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="F30" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="G30" s="4"/>
       <c r="I30">
@@ -7065,10 +7049,10 @@
         <v>44984.4097453704</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="F31" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="G31" s="5"/>
       <c r="I31">
@@ -7092,13 +7076,13 @@
         <v>44984.4097453704</v>
       </c>
       <c r="E32" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="F32" t="s">
+        <v>314</v>
+      </c>
+      <c r="G32" s="5" t="s">
         <v>315</v>
-      </c>
-      <c r="F32" t="s">
-        <v>316</v>
-      </c>
-      <c r="G32" s="5" t="s">
-        <v>317</v>
       </c>
       <c r="I32">
         <v>10</v>
@@ -7121,10 +7105,10 @@
         <v>44984.4097453704</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F33" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="G33" s="5">
         <v>25</v>
@@ -7183,13 +7167,13 @@
         <v>133</v>
       </c>
       <c r="G1" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="H1" t="s">
         <v>146</v>
       </c>
       <c r="I1" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -7206,7 +7190,7 @@
         <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="G2" t="s">
         <v>38</v>
@@ -7232,7 +7216,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="G3" t="s">
         <v>38</v>
